--- a/docs/plantillas/registro_desayuno_operativo_LISTA_ACTUALIZADA_ACTUALIZADA.xlsx
+++ b/docs/plantillas/registro_desayuno_operativo_LISTA_ACTUALIZADA_ACTUALIZADA.xlsx
@@ -503,6 +503,9 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -520,173 +523,223 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2. En cada línea ponga la Fecha (AAAA-MM-DD). Misma fecha = un solo desayuno en BM.</t>
+          <t>2. En cada línea ponga la Fecha (AAAA-MM-DD). Misma fecha = UN solo desayuno en BM.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3. Huespedes: basta en la primera línea de ese día (si vacío, se cuenta 1 por línea Receta).</t>
+          <t>3. Huéspedes (por línea, se SUMAN en el día):</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4. Tipo: Receta (plato/bebida), Extra (buffet rápido) o Producto (mismo catálogo de extras).</t>
+          <t xml:space="preserve">   • 1 = nuevo comensal (cuenta 1 persona).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5. Nombre: elija del desplegable (lista en hoja Catalogo).</t>
+          <t xml:space="preserve">   • 0 = mismo comensal que pide otro plato (NO suma persona).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6. Cantidad ↑↓: raciones o unidades. Escriba un número 1–30.</t>
+          <t xml:space="preserve">   • Vacío = igual que 0 (no suma).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7. Extra1…Extra4: extras sobre una Receta (bacon, aguacate, huevo, pan, etc.).</t>
+          <t xml:space="preserve">   Ejemplo: comensal pide inglés + café → fila inglés Huespedes=1, fila café=0.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8. Omitir1/Omitir2: quitar un ingrediente (Bacon, Sin huevo, Sin tostada…).</t>
+          <t xml:space="preserve">   Total del día = suma de la columna (solo los 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Tipo: Receta (plato/bebida), Extra (buffet rápido) o Producto.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HUEVOS (Desayuno inglés)</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5. Nombre: elija del desplegable (lista en hoja Catalogo).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>• La ficha «Desayuno ingles» incluye Huevo frito por defecto.</t>
+          <t>6. Cantidad ↑↓: raciones o unidades de ESA línea (1–30).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>• Para otro tipo: Extra1 = Huevo pochado / Huevos revueltos / Huevo cocido</t>
+          <t>7. Extra1…Extra4: extras sobre una Receta (bacon, aguacate, huevo, pan…).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (sustituye al frito; no sume un segundo huevo).</t>
+          <t>8. Omitir1/Omitir2: quitar un ingrediente (Bacon, Sin huevo, Sin tostada…).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>• Para sin huevo: Omitir1 = Sin huevo (o Huevo frito).</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>• Para huevo suelto (no inglés): Tipo=Receta y Nombre=Huevo frito / pochado / …</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANTE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  o Tipo=Extra y Nombre=Huevo frito (añade al buffet).</t>
+          <t>• No ponga 1 en todas las filas: si lo hace, contará 1 huésped por plato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>• Cantidad es raciones del plato, no el número de huéspedes.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>PAN (tostadas / sándwiches)</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>• Tras importar, puede borrar las filas del Excel; en BM ya queda el registro.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>• Por defecto las fichas llevan molde común (blanco) = «Tostada» / «Pan blanco».</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>• Para integral: Extra1 = Tostada integral (o Pan integral).</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>HUEVOS (Desayuno inglés)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>• Para sin gluten: Extra1 = Tostada sin gluten (o Pan sin gluten)</t>
+          <t>• La ficha «Desayuno ingles» incluye Huevo frito por defecto.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  → panecillo s/gluten Betina; sustituye el pan de la ficha (1 reb → 1 ud).</t>
+          <t>• Para otro tipo: Extra1 = Huevo pochado / Huevos revueltos / Huevo cocido</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>• Para volver a blanco: Extra1 = Tostada / Pan blanco.</t>
+          <t xml:space="preserve">  (sustituye al frito; no sume un segundo huevo).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>• Sin pan: Omitir1 = Sin tostada.</t>
+          <t>• Para sin huevo: Omitir1 = Sin huevo (o Huevo frito).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>• Pan suelto de buffet: Tipo=Extra y Nombre=Tostada / integral / sin gluten.</t>
-        </is>
-      </c>
+          <t>• Huevo suelto: Tipo=Receta y Nombre=Huevo frito / pochado / …</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>9. Guarde el archivo y ejecute el importador (ver 2_importar_a_bm.cmd).</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PAN (tostadas / sándwiches)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10. Use --dry-run primero. La columna Importado la rellena el script.</t>
+          <t>• Por defecto: molde común (blanco) = Tostada / Pan blanco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>• Integral: Extra1 = Tostada integral (o Pan integral).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
+        <is>
+          <t>• Sin gluten: Extra1 = Tostada sin gluten (o Pan sin gluten).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>• Sin pan: Omitir1 = Sin tostada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9. Guarde y ejecute 2_importar_a_bm.cmd (mejor --dry-run antes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10. La columna Importado la rellena el script (no la edite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Al regenerar la plantilla NO se borran las filas ya rellenadas en Registro.</t>
         </is>
@@ -866,7 +919,7 @@
       <c r="P2" s="7" t="n"/>
       <c r="Q2" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -903,7 +956,7 @@
       <c r="P3" s="7" t="n"/>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -946,7 +999,7 @@
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -983,7 +1036,7 @@
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1079,7 @@
       <c r="P6" s="7" t="n"/>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1124,7 @@
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1161,7 @@
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1210,7 @@
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1257,7 @@
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1294,7 @@
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1331,7 @@
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1368,7 @@
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1405,7 @@
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1442,7 @@
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1479,7 @@
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1534,7 @@
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1577,7 @@
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1626,7 @@
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1673,7 @@
       <c r="P20" s="7" t="n"/>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1716,7 @@
       <c r="P21" s="7" t="n"/>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1777,7 @@
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1838,7 @@
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1887,7 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1930,7 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1991,7 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -1981,7 +2034,7 @@
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2077,7 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2114,7 @@
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2163,7 @@
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2212,7 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>OK d151, d152, d153, d154, d155, d156, d157, d158, d159, d160, d161, d162, d163, d164, d165, d166, d167, d168, d169, d170, d171, d172, d173, d174, d175, d176, d177, d178, d179, d180</t>
+          <t>OK d181</t>
         </is>
       </c>
     </row>

--- a/docs/plantillas/registro_desayuno_operativo_LISTA_ACTUALIZADA_ACTUALIZADA.xlsx
+++ b/docs/plantillas/registro_desayuno_operativo_LISTA_ACTUALIZADA_ACTUALIZADA.xlsx
@@ -15,11 +15,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConsumoBuffet" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegistroComida" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegistroCena" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegistroBebidasDesayuno" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Registro'!$A$1:$Q$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'RegistroComida'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'RegistroCena'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'RegistroBebidasDesayuno'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -507,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -772,7 +774,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Recetas desayuno: 39 | Extras: 56</t>
+          <t>Recetas desayuno: 40 | Extras: 56</t>
         </is>
       </c>
     </row>
@@ -782,28 +784,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CONSUMO BUFFET (hoja ConsumoBuffet)</t>
+          <t>BEBIDAS DESAYUNO (hoja RegistroBebidasDesayuno)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>• Concepto: elija de ConfigBuffet (editable). Motivo: Consumo / Merma / Expiración / Limpieza.</t>
+          <t>• Cafés, tés, Cola Cao, Cava Roger de Flor, etc. (catálogo columna I).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>• Jarra zumo naranja: rellene Naranjas (b06) y ZumoBote (b28) si aplica.</t>
+          <t>• Misma Fecha = un registro de bebidas en BM.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>• Columna Coste usa Precios × cantidades (referencia; el import recalcula en BM).</t>
+          <t>• Tipo: Receta (café, cava…) o Producto (botella suelta). Cantidad: raciones/unidades.</t>
         </is>
       </c>
     </row>
@@ -820,7 +822,31 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Comida: 0 | Cena: 0 | Buffet: 0 fila(s) preservadas.</t>
+          <t>Comida: 0 | Cena: 0 | Bebidas: 0 | Buffet: 230 fila(s) preservadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>• Jarra zumo naranja: rellene Naranjas (b06) y ZumoBote (b28) si aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>• Columna Coste usa Precios × cantidades (referencia; el import recalcula en BM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Al regenerar la plantilla NO se borran filas ya rellenadas en hojas de registro.</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5594,7 @@
       <formula1>"Receta,Extra,Producto"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Catalogo!$C$2:$C$92</formula1>
+      <formula1>Catalogo!$C$2:$C$93</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F500 H2:H500 J2:J500 L2:L500 N2:N500 O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Catalogo!$E$2:$E$59</formula1>
@@ -5588,7 +5614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5599,6 +5625,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5642,6 +5669,11 @@
           <t>Recetas_cena</t>
         </is>
       </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Bebidas_desayuno</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -5684,11 +5716,16 @@
           <t>Absolut</t>
         </is>
       </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Americano</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Cafe con leche</t>
+          <t>Botella Roger de Flor</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5698,7 +5735,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cafe con leche</t>
+          <t>Botella Roger de Flor</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5724,13 +5761,18 @@
       <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Amaretto</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Botella Roger de Flor</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Cafe con leche descafeinado</t>
+          <t>Cafe con leche</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5740,7 +5782,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cafe con leche descafeinado</t>
+          <t>Cafe con leche</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5766,13 +5808,18 @@
       <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Americano</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Cafe con leche</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Cafe con leche semi</t>
+          <t>Cafe con leche descafeinado</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5782,7 +5829,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cafe con leche semi</t>
+          <t>Cafe con leche descafeinado</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -5808,13 +5855,18 @@
       <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Aperol</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Cafe con leche descafeinado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Capuchino</t>
+          <t>Cafe con leche semi</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5824,7 +5876,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Capuchino</t>
+          <t>Cafe con leche semi</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -5850,13 +5902,18 @@
       <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Aperol Spritz</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Cafe con leche semi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Capuchino semi</t>
+          <t>Capuchino</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5866,7 +5923,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Capuchino semi</t>
+          <t>Capuchino</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -5887,13 +5944,18 @@
       <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Baileys</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Capuchino</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Cola Cao</t>
+          <t>Capuchino semi</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5903,7 +5965,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cola Cao</t>
+          <t>Capuchino semi</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -5924,13 +5986,18 @@
       <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Beefeater</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Capuchino semi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Cola Cao semi</t>
+          <t>Cola Cao</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5940,7 +6007,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cola Cao semi</t>
+          <t>Cola Cao</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -5956,13 +6023,18 @@
       <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Blue Hawaii</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Cava Roger de Flor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Cortado</t>
+          <t>Cola Cao semi</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5972,7 +6044,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cortado</t>
+          <t>Cola Cao semi</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -5988,13 +6060,18 @@
       <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Botella Anna Codorniu Mini</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Cola Cao</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Cortado semi</t>
+          <t>Cortado</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -6004,7 +6081,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cortado semi</t>
+          <t>Cortado</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -6020,13 +6097,18 @@
       <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Botella Codorniu Prima Vides</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Cola Cao semi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Desayuno ingles</t>
+          <t>Cortado semi</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -6036,7 +6118,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Desayuno ingles</t>
+          <t>Cortado semi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6052,13 +6134,18 @@
       <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Botella Ederra</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Cortado</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Espresso</t>
+          <t>Desayuno ingles</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -6068,7 +6155,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Espresso</t>
+          <t>Desayuno ingles</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6084,13 +6171,18 @@
       <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Botella El Grifo</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Cortado semi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Espresso descafeinado</t>
+          <t>Espresso</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -6100,7 +6192,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Espresso descafeinado</t>
+          <t>Espresso</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6116,13 +6208,18 @@
       <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Botella Montecillo Blanco</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Espresso</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Estándar buffet desayuno diario</t>
+          <t>Espresso descafeinado</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -6132,7 +6229,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estándar buffet desayuno diario</t>
+          <t>Espresso descafeinado</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6148,13 +6245,18 @@
       <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Botella Montecillo Crianza</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Espresso descafeinado</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Huevo cocido</t>
+          <t>Estándar buffet desayuno diario</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -6164,7 +6266,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Huevo cocido</t>
+          <t>Estándar buffet desayuno diario</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6180,13 +6282,18 @@
       <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Botella Montecillo Reserva</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>HELADO CHOCOLATE 5L</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Huevo frito</t>
+          <t>Huevo cocido</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6196,7 +6303,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Huevo frito</t>
+          <t>Huevo cocido</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6212,13 +6319,18 @@
       <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Botella Montecillo Rosado</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>HELADO VAINILLA 5L</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Huevo pochado</t>
+          <t>Huevo frito</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6228,7 +6340,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Huevo pochado</t>
+          <t>Huevo frito</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6244,13 +6356,18 @@
       <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Botella Piper Heidsieck Brut</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Manzanilla</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Huevos revueltos</t>
+          <t>Huevo pochado</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6260,7 +6377,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Huevos revueltos</t>
+          <t>Huevo pochado</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6276,13 +6393,18 @@
       <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Botella Piper Heidsieck Rose</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Seleccion de te</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Huevos rotos</t>
+          <t>Huevos revueltos</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6292,7 +6414,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Huevos rotos</t>
+          <t>Huevos revueltos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6308,13 +6430,18 @@
       <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Botella Roger de Flor</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>SMOOTHIE B6 PITA-MANG-FRESA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Manzanilla</t>
+          <t>Huevos rotos</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6324,7 +6451,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manzanilla</t>
+          <t>Huevos rotos</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6340,13 +6467,18 @@
       <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Cafe Baileys</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>SMOOTHIES VIERA B7 COLADA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Sandwich de la casa</t>
+          <t>Manzanilla</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6356,7 +6488,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandwich de la casa</t>
+          <t>Manzanilla</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6372,13 +6504,18 @@
       <c r="H22" s="9" t="inlineStr">
         <is>
           <t>Cafe con leche</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Te frutas del bosque</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Sandwich mixto</t>
+          <t>Sandwich de la casa</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6388,7 +6525,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sandwich mixto</t>
+          <t>Sandwich de la casa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6404,13 +6541,18 @@
       <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Cafe con leche descafeinado</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Te negro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Sandwich vegetal</t>
+          <t>Sandwich mixto</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6420,7 +6562,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sandwich vegetal</t>
+          <t>Sandwich mixto</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -6436,13 +6578,18 @@
       <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Cafe con leche semi</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Te rojo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Seleccion de te</t>
+          <t>Sandwich vegetal</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6452,7 +6599,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seleccion de te</t>
+          <t>Sandwich vegetal</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -6468,13 +6615,18 @@
       <c r="H25" s="9" t="inlineStr">
         <is>
           <t>Cafe irlandes</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Te verde</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Te frutas del bosque</t>
+          <t>Seleccion de te</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6484,7 +6636,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Te frutas del bosque</t>
+          <t>Seleccion de te</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -6506,7 +6658,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Te negro</t>
+          <t>Te frutas del bosque</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6516,7 +6668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Te negro</t>
+          <t>Te frutas del bosque</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -6538,7 +6690,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Te rojo</t>
+          <t>Te negro</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6548,7 +6700,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Te rojo</t>
+          <t>Te negro</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6570,7 +6722,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Te verde</t>
+          <t>Te rojo</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6580,7 +6732,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Te verde</t>
+          <t>Te rojo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6602,7 +6754,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Tortilla</t>
+          <t>Te verde</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6612,7 +6764,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tortilla</t>
+          <t>Te verde</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6634,7 +6786,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Tostada champinones</t>
+          <t>Tortilla</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6644,7 +6796,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tostada champinones</t>
+          <t>Tortilla</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6666,7 +6818,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Tostada del dia</t>
+          <t>Tostada champinones</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6676,7 +6828,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tostada del dia</t>
+          <t>Tostada champinones</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6698,7 +6850,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Tostada domingo</t>
+          <t>Tostada del dia</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6708,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tostada domingo</t>
+          <t>Tostada del dia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6730,7 +6882,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Tostada francesa</t>
+          <t>Tostada domingo</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6740,7 +6892,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tostada francesa</t>
+          <t>Tostada domingo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6762,7 +6914,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Tostada jueves</t>
+          <t>Tostada francesa</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6772,7 +6924,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tostada jueves</t>
+          <t>Tostada francesa</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6794,7 +6946,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Tostada lunes</t>
+          <t>Tostada jueves</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6804,7 +6956,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tostada lunes</t>
+          <t>Tostada jueves</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6826,7 +6978,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Tostada martes</t>
+          <t>Tostada lunes</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6836,7 +6988,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tostada martes</t>
+          <t>Tostada lunes</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6858,7 +7010,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Tostada miercoles</t>
+          <t>Tostada martes</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6868,7 +7020,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tostada miercoles</t>
+          <t>Tostada martes</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6890,7 +7042,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Tostada sabado</t>
+          <t>Tostada miercoles</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6900,7 +7052,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tostada sabado</t>
+          <t>Tostada miercoles</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6922,44 +7074,49 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
+          <t>Tostada sabado</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Queso gofio</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tostada sabado</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Queso gofio</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Copa de sangria</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Cortado semi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
           <t>Tostada viernes</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Queso gofio</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Queso pimenton</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Tostada viernes</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Queso gofio</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>Copa de sangria</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>Cortado semi</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Queso pimenton</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Queso cheddar</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6986,7 +7143,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Queso gouda</t>
+          <t>Queso cheddar</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -7013,7 +7170,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Queso gouda</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7040,7 +7197,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamon cocido</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7067,7 +7224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tostada</t>
+          <t>Jamon cocido</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7094,7 +7251,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tostada integral</t>
+          <t>Tostada</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7121,7 +7278,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pan blanco</t>
+          <t>Tostada integral</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -7148,7 +7305,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pan integral</t>
+          <t>Pan blanco</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7175,7 +7332,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tostada sin gluten</t>
+          <t>Pan integral</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -7202,7 +7359,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pan sin gluten</t>
+          <t>Tostada sin gluten</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7229,7 +7386,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salchicha</t>
+          <t>Pan sin gluten</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7256,7 +7413,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hashbrown</t>
+          <t>Salchicha</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7283,7 +7440,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Champi</t>
+          <t>Hashbrown</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7310,7 +7467,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aguacate</t>
+          <t>Champi</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7337,7 +7494,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Aguacate</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7364,7 +7521,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7391,7 +7548,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7413,7 +7570,7 @@
     <row r="58">
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alubias</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -7435,7 +7592,7 @@
     <row r="59">
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pimiento</t>
+          <t>Alubias</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -7457,7 +7614,7 @@
     <row r="60">
       <c r="C60" t="inlineStr">
         <is>
-          <t>Espinacas</t>
+          <t>Pimiento</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -7474,7 +7631,7 @@
     <row r="61">
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tomate cherry</t>
+          <t>Espinacas</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -7491,7 +7648,7 @@
     <row r="62">
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Tomate cherry</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -7508,7 +7665,7 @@
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -7525,7 +7682,7 @@
     <row r="64">
       <c r="C64" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Kiwi</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -7542,7 +7699,7 @@
     <row r="65">
       <c r="C65" t="inlineStr">
         <is>
-          <t>Melon</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -7559,7 +7716,7 @@
     <row r="66">
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sandia</t>
+          <t>Melon</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
@@ -7576,7 +7733,7 @@
     <row r="67">
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pomelo</t>
+          <t>Sandia</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -7593,7 +7750,7 @@
     <row r="68">
       <c r="C68" t="inlineStr">
         <is>
-          <t>Naranja</t>
+          <t>Pomelo</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -7610,7 +7767,7 @@
     <row r="69">
       <c r="C69" t="inlineStr">
         <is>
-          <t>Platano</t>
+          <t>Naranja</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -7627,7 +7784,7 @@
     <row r="70">
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pina</t>
+          <t>Platano</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -7644,7 +7801,7 @@
     <row r="71">
       <c r="C71" t="inlineStr">
         <is>
-          <t>Melocoton almibar</t>
+          <t>Pina</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -7661,7 +7818,7 @@
     <row r="72">
       <c r="C72" t="inlineStr">
         <is>
-          <t>Paleta iberica</t>
+          <t>Melocoton almibar</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -7678,7 +7835,7 @@
     <row r="73">
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mortadela</t>
+          <t>Paleta iberica</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
@@ -7695,7 +7852,7 @@
     <row r="74">
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salchichon iberico</t>
+          <t>Mortadela</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
@@ -7712,7 +7869,7 @@
     <row r="75">
       <c r="C75" t="inlineStr">
         <is>
-          <t>Queso gofio</t>
+          <t>Salchichon iberico</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -7729,7 +7886,7 @@
     <row r="76">
       <c r="C76" t="inlineStr">
         <is>
-          <t>Queso pimenton</t>
+          <t>Queso gofio</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -7746,7 +7903,7 @@
     <row r="77">
       <c r="C77" t="inlineStr">
         <is>
-          <t>Queso fresco</t>
+          <t>Queso pimenton</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
@@ -7763,7 +7920,7 @@
     <row r="78">
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pan gallego</t>
+          <t>Queso fresco</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
@@ -7775,7 +7932,7 @@
     <row r="79">
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pan maiz</t>
+          <t>Pan gallego</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
@@ -7787,7 +7944,7 @@
     <row r="80">
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pan centeno</t>
+          <t>Pan maiz</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
@@ -7799,7 +7956,7 @@
     <row r="81">
       <c r="C81" t="inlineStr">
         <is>
-          <t>Baguettina</t>
+          <t>Pan centeno</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -7811,7 +7968,7 @@
     <row r="82">
       <c r="C82" t="inlineStr">
         <is>
-          <t>Napolitana cacao</t>
+          <t>Baguettina</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
@@ -7823,7 +7980,7 @@
     <row r="83">
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chic crema</t>
+          <t>Napolitana cacao</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
@@ -7835,7 +7992,7 @@
     <row r="84">
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lazo cereal</t>
+          <t>Chic crema</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
@@ -7847,7 +8004,7 @@
     <row r="85">
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croissant mantequilla</t>
+          <t>Lazo cereal</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
@@ -7859,7 +8016,7 @@
     <row r="86">
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croissant chocolate</t>
+          <t>Croissant mantequilla</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
@@ -7871,7 +8028,7 @@
     <row r="87">
       <c r="C87" t="inlineStr">
         <is>
-          <t>Surtido reposteria</t>
+          <t>Croissant chocolate</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
@@ -7883,7 +8040,7 @@
     <row r="88">
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leche entera</t>
+          <t>Surtido reposteria</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
@@ -7895,7 +8052,7 @@
     <row r="89">
       <c r="C89" t="inlineStr">
         <is>
-          <t>Leche semi</t>
+          <t>Leche entera</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -7907,7 +8064,7 @@
     <row r="90">
       <c r="C90" t="inlineStr">
         <is>
-          <t>Leche de avena</t>
+          <t>Leche semi</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
@@ -7919,7 +8076,7 @@
     <row r="91">
       <c r="C91" t="inlineStr">
         <is>
-          <t>Leche de soja</t>
+          <t>Leche de avena</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -7931,16 +8088,21 @@
     <row r="92">
       <c r="C92" t="inlineStr">
         <is>
+          <t>Leche de soja</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>Smirnoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" t="inlineStr">
+        <is>
           <t>Leche de almendras</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>Smirnoff</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
       <c r="G93" s="9" t="inlineStr">
         <is>
           <t>Tanqueray</t>
@@ -17249,7 +17411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19536,14 +19698,2452 @@
       <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
     </row>
+    <row r="150">
+      <c r="A150" s="7" t="n"/>
+      <c r="B150" s="7" t="n"/>
+      <c r="C150" s="7" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="E150" s="7" t="n"/>
+      <c r="F150" s="7" t="n"/>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H150" s="7">
+        <f>SUM(H2:H150)</f>
+        <v/>
+      </c>
+      <c r="I150" s="7" t="n"/>
+      <c r="J150" s="7" t="n"/>
+    </row>
     <row r="151">
-      <c r="G151" s="13" t="inlineStr">
+      <c r="A151" s="7" t="n"/>
+      <c r="B151" s="7" t="n"/>
+      <c r="C151" s="7" t="n"/>
+      <c r="D151" s="7" t="n"/>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="7" t="n"/>
+      <c r="G151" s="7" t="n"/>
+      <c r="H151" s="7">
+        <f>IF(E151="Consumo",IFERROR(D151*VLOOKUP(VLOOKUP(C151,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C151,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F151*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G151*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I151" s="7" t="n"/>
+      <c r="J151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n"/>
+      <c r="B152" s="7" t="n"/>
+      <c r="C152" s="7" t="n"/>
+      <c r="D152" s="7" t="n"/>
+      <c r="E152" s="7" t="n"/>
+      <c r="F152" s="7" t="n"/>
+      <c r="G152" s="7" t="n"/>
+      <c r="H152" s="7">
+        <f>IF(E152="Consumo",IFERROR(D152*VLOOKUP(VLOOKUP(C152,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C152,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F152*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G152*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I152" s="7" t="n"/>
+      <c r="J152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="n"/>
+      <c r="B153" s="7" t="n"/>
+      <c r="C153" s="7" t="n"/>
+      <c r="D153" s="7" t="n"/>
+      <c r="E153" s="7" t="n"/>
+      <c r="F153" s="7" t="n"/>
+      <c r="G153" s="7" t="n"/>
+      <c r="H153" s="7">
+        <f>IF(E153="Consumo",IFERROR(D153*VLOOKUP(VLOOKUP(C153,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C153,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F153*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G153*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I153" s="7" t="n"/>
+      <c r="J153" s="7" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="n"/>
+      <c r="B154" s="7" t="n"/>
+      <c r="C154" s="7" t="n"/>
+      <c r="D154" s="7" t="n"/>
+      <c r="E154" s="7" t="n"/>
+      <c r="F154" s="7" t="n"/>
+      <c r="G154" s="7" t="n"/>
+      <c r="H154" s="7">
+        <f>IF(E154="Consumo",IFERROR(D154*VLOOKUP(VLOOKUP(C154,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C154,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F154*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G154*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I154" s="7" t="n"/>
+      <c r="J154" s="7" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="n"/>
+      <c r="B155" s="7" t="n"/>
+      <c r="C155" s="7" t="n"/>
+      <c r="D155" s="7" t="n"/>
+      <c r="E155" s="7" t="n"/>
+      <c r="F155" s="7" t="n"/>
+      <c r="G155" s="7" t="n"/>
+      <c r="H155" s="7">
+        <f>IF(E155="Consumo",IFERROR(D155*VLOOKUP(VLOOKUP(C155,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C155,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F155*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G155*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I155" s="7" t="n"/>
+      <c r="J155" s="7" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n"/>
+      <c r="B156" s="7" t="n"/>
+      <c r="C156" s="7" t="n"/>
+      <c r="D156" s="7" t="n"/>
+      <c r="E156" s="7" t="n"/>
+      <c r="F156" s="7" t="n"/>
+      <c r="G156" s="7" t="n"/>
+      <c r="H156" s="7">
+        <f>IF(E156="Consumo",IFERROR(D156*VLOOKUP(VLOOKUP(C156,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C156,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F156*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G156*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I156" s="7" t="n"/>
+      <c r="J156" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="n"/>
+      <c r="B157" s="7" t="n"/>
+      <c r="C157" s="7" t="n"/>
+      <c r="D157" s="7" t="n"/>
+      <c r="E157" s="7" t="n"/>
+      <c r="F157" s="7" t="n"/>
+      <c r="G157" s="7" t="n"/>
+      <c r="H157" s="7">
+        <f>IF(E157="Consumo",IFERROR(D157*VLOOKUP(VLOOKUP(C157,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C157,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F157*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G157*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I157" s="7" t="n"/>
+      <c r="J157" s="7" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="n"/>
+      <c r="B158" s="7" t="n"/>
+      <c r="C158" s="7" t="n"/>
+      <c r="D158" s="7" t="n"/>
+      <c r="E158" s="7" t="n"/>
+      <c r="F158" s="7" t="n"/>
+      <c r="G158" s="7" t="n"/>
+      <c r="H158" s="7">
+        <f>IF(E158="Consumo",IFERROR(D158*VLOOKUP(VLOOKUP(C158,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C158,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F158*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G158*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I158" s="7" t="n"/>
+      <c r="J158" s="7" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="n"/>
+      <c r="B159" s="7" t="n"/>
+      <c r="C159" s="7" t="n"/>
+      <c r="D159" s="7" t="n"/>
+      <c r="E159" s="7" t="n"/>
+      <c r="F159" s="7" t="n"/>
+      <c r="G159" s="7" t="n"/>
+      <c r="H159" s="7">
+        <f>IF(E159="Consumo",IFERROR(D159*VLOOKUP(VLOOKUP(C159,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C159,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F159*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G159*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I159" s="7" t="n"/>
+      <c r="J159" s="7" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="n"/>
+      <c r="B160" s="7" t="n"/>
+      <c r="C160" s="7" t="n"/>
+      <c r="D160" s="7" t="n"/>
+      <c r="E160" s="7" t="n"/>
+      <c r="F160" s="7" t="n"/>
+      <c r="G160" s="7" t="n"/>
+      <c r="H160" s="7">
+        <f>IF(E160="Consumo",IFERROR(D160*VLOOKUP(VLOOKUP(C160,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C160,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F160*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G160*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I160" s="7" t="n"/>
+      <c r="J160" s="7" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="n"/>
+      <c r="B161" s="7" t="n"/>
+      <c r="C161" s="7" t="n"/>
+      <c r="D161" s="7" t="n"/>
+      <c r="E161" s="7" t="n"/>
+      <c r="F161" s="7" t="n"/>
+      <c r="G161" s="7" t="n"/>
+      <c r="H161" s="7">
+        <f>IF(E161="Consumo",IFERROR(D161*VLOOKUP(VLOOKUP(C161,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C161,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F161*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G161*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I161" s="7" t="n"/>
+      <c r="J161" s="7" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="n"/>
+      <c r="B162" s="7" t="n"/>
+      <c r="C162" s="7" t="n"/>
+      <c r="D162" s="7" t="n"/>
+      <c r="E162" s="7" t="n"/>
+      <c r="F162" s="7" t="n"/>
+      <c r="G162" s="7" t="n"/>
+      <c r="H162" s="7">
+        <f>IF(E162="Consumo",IFERROR(D162*VLOOKUP(VLOOKUP(C162,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C162,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F162*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G162*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I162" s="7" t="n"/>
+      <c r="J162" s="7" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="n"/>
+      <c r="B163" s="7" t="n"/>
+      <c r="C163" s="7" t="n"/>
+      <c r="D163" s="7" t="n"/>
+      <c r="E163" s="7" t="n"/>
+      <c r="F163" s="7" t="n"/>
+      <c r="G163" s="7" t="n"/>
+      <c r="H163" s="7">
+        <f>IF(E163="Consumo",IFERROR(D163*VLOOKUP(VLOOKUP(C163,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C163,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F163*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G163*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I163" s="7" t="n"/>
+      <c r="J163" s="7" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="n"/>
+      <c r="B164" s="7" t="n"/>
+      <c r="C164" s="7" t="n"/>
+      <c r="D164" s="7" t="n"/>
+      <c r="E164" s="7" t="n"/>
+      <c r="F164" s="7" t="n"/>
+      <c r="G164" s="7" t="n"/>
+      <c r="H164" s="7">
+        <f>IF(E164="Consumo",IFERROR(D164*VLOOKUP(VLOOKUP(C164,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C164,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F164*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G164*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I164" s="7" t="n"/>
+      <c r="J164" s="7" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="n"/>
+      <c r="B165" s="7" t="n"/>
+      <c r="C165" s="7" t="n"/>
+      <c r="D165" s="7" t="n"/>
+      <c r="E165" s="7" t="n"/>
+      <c r="F165" s="7" t="n"/>
+      <c r="G165" s="7" t="n"/>
+      <c r="H165" s="7">
+        <f>IF(E165="Consumo",IFERROR(D165*VLOOKUP(VLOOKUP(C165,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C165,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F165*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G165*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I165" s="7" t="n"/>
+      <c r="J165" s="7" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n"/>
+      <c r="B166" s="7" t="n"/>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
+      <c r="E166" s="7" t="n"/>
+      <c r="F166" s="7" t="n"/>
+      <c r="G166" s="7" t="n"/>
+      <c r="H166" s="7">
+        <f>IF(E166="Consumo",IFERROR(D166*VLOOKUP(VLOOKUP(C166,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C166,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F166*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G166*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I166" s="7" t="n"/>
+      <c r="J166" s="7" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="n"/>
+      <c r="B167" s="7" t="n"/>
+      <c r="C167" s="7" t="n"/>
+      <c r="D167" s="7" t="n"/>
+      <c r="E167" s="7" t="n"/>
+      <c r="F167" s="7" t="n"/>
+      <c r="G167" s="7" t="n"/>
+      <c r="H167" s="7">
+        <f>IF(E167="Consumo",IFERROR(D167*VLOOKUP(VLOOKUP(C167,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C167,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F167*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G167*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I167" s="7" t="n"/>
+      <c r="J167" s="7" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n"/>
+      <c r="B168" s="7" t="n"/>
+      <c r="C168" s="7" t="n"/>
+      <c r="D168" s="7" t="n"/>
+      <c r="E168" s="7" t="n"/>
+      <c r="F168" s="7" t="n"/>
+      <c r="G168" s="7" t="n"/>
+      <c r="H168" s="7">
+        <f>IF(E168="Consumo",IFERROR(D168*VLOOKUP(VLOOKUP(C168,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C168,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F168*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G168*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I168" s="7" t="n"/>
+      <c r="J168" s="7" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="n"/>
+      <c r="B169" s="7" t="n"/>
+      <c r="C169" s="7" t="n"/>
+      <c r="D169" s="7" t="n"/>
+      <c r="E169" s="7" t="n"/>
+      <c r="F169" s="7" t="n"/>
+      <c r="G169" s="7" t="n"/>
+      <c r="H169" s="7">
+        <f>IF(E169="Consumo",IFERROR(D169*VLOOKUP(VLOOKUP(C169,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C169,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F169*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G169*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I169" s="7" t="n"/>
+      <c r="J169" s="7" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n"/>
+      <c r="B170" s="7" t="n"/>
+      <c r="C170" s="7" t="n"/>
+      <c r="D170" s="7" t="n"/>
+      <c r="E170" s="7" t="n"/>
+      <c r="F170" s="7" t="n"/>
+      <c r="G170" s="7" t="n"/>
+      <c r="H170" s="7">
+        <f>IF(E170="Consumo",IFERROR(D170*VLOOKUP(VLOOKUP(C170,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C170,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F170*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G170*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I170" s="7" t="n"/>
+      <c r="J170" s="7" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="n"/>
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="7" t="n"/>
+      <c r="D171" s="7" t="n"/>
+      <c r="E171" s="7" t="n"/>
+      <c r="F171" s="7" t="n"/>
+      <c r="G171" s="7" t="n"/>
+      <c r="H171" s="7">
+        <f>IF(E171="Consumo",IFERROR(D171*VLOOKUP(VLOOKUP(C171,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C171,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F171*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G171*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I171" s="7" t="n"/>
+      <c r="J171" s="7" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="n"/>
+      <c r="B172" s="7" t="n"/>
+      <c r="C172" s="7" t="n"/>
+      <c r="D172" s="7" t="n"/>
+      <c r="E172" s="7" t="n"/>
+      <c r="F172" s="7" t="n"/>
+      <c r="G172" s="7" t="n"/>
+      <c r="H172" s="7">
+        <f>IF(E172="Consumo",IFERROR(D172*VLOOKUP(VLOOKUP(C172,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C172,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F172*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G172*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I172" s="7" t="n"/>
+      <c r="J172" s="7" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="n"/>
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="7" t="n"/>
+      <c r="D173" s="7" t="n"/>
+      <c r="E173" s="7" t="n"/>
+      <c r="F173" s="7" t="n"/>
+      <c r="G173" s="7" t="n"/>
+      <c r="H173" s="7">
+        <f>IF(E173="Consumo",IFERROR(D173*VLOOKUP(VLOOKUP(C173,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C173,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F173*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G173*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I173" s="7" t="n"/>
+      <c r="J173" s="7" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="n"/>
+      <c r="B174" s="7" t="n"/>
+      <c r="C174" s="7" t="n"/>
+      <c r="D174" s="7" t="n"/>
+      <c r="E174" s="7" t="n"/>
+      <c r="F174" s="7" t="n"/>
+      <c r="G174" s="7" t="n"/>
+      <c r="H174" s="7">
+        <f>IF(E174="Consumo",IFERROR(D174*VLOOKUP(VLOOKUP(C174,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C174,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F174*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G174*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I174" s="7" t="n"/>
+      <c r="J174" s="7" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="n"/>
+      <c r="B175" s="7" t="n"/>
+      <c r="C175" s="7" t="n"/>
+      <c r="D175" s="7" t="n"/>
+      <c r="E175" s="7" t="n"/>
+      <c r="F175" s="7" t="n"/>
+      <c r="G175" s="7" t="n"/>
+      <c r="H175" s="7">
+        <f>IF(E175="Consumo",IFERROR(D175*VLOOKUP(VLOOKUP(C175,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C175,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F175*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G175*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I175" s="7" t="n"/>
+      <c r="J175" s="7" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="n"/>
+      <c r="B176" s="7" t="n"/>
+      <c r="C176" s="7" t="n"/>
+      <c r="D176" s="7" t="n"/>
+      <c r="E176" s="7" t="n"/>
+      <c r="F176" s="7" t="n"/>
+      <c r="G176" s="7" t="n"/>
+      <c r="H176" s="7">
+        <f>IF(E176="Consumo",IFERROR(D176*VLOOKUP(VLOOKUP(C176,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C176,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F176*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G176*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I176" s="7" t="n"/>
+      <c r="J176" s="7" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="n"/>
+      <c r="B177" s="7" t="n"/>
+      <c r="C177" s="7" t="n"/>
+      <c r="D177" s="7" t="n"/>
+      <c r="E177" s="7" t="n"/>
+      <c r="F177" s="7" t="n"/>
+      <c r="G177" s="7" t="n"/>
+      <c r="H177" s="7">
+        <f>IF(E177="Consumo",IFERROR(D177*VLOOKUP(VLOOKUP(C177,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C177,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F177*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G177*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I177" s="7" t="n"/>
+      <c r="J177" s="7" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="n"/>
+      <c r="B178" s="7" t="n"/>
+      <c r="C178" s="7" t="n"/>
+      <c r="D178" s="7" t="n"/>
+      <c r="E178" s="7" t="n"/>
+      <c r="F178" s="7" t="n"/>
+      <c r="G178" s="7" t="n"/>
+      <c r="H178" s="7">
+        <f>IF(E178="Consumo",IFERROR(D178*VLOOKUP(VLOOKUP(C178,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C178,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F178*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G178*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I178" s="7" t="n"/>
+      <c r="J178" s="7" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="n"/>
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="7" t="n"/>
+      <c r="D179" s="7" t="n"/>
+      <c r="E179" s="7" t="n"/>
+      <c r="F179" s="7" t="n"/>
+      <c r="G179" s="7" t="n"/>
+      <c r="H179" s="7">
+        <f>IF(E179="Consumo",IFERROR(D179*VLOOKUP(VLOOKUP(C179,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C179,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F179*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G179*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I179" s="7" t="n"/>
+      <c r="J179" s="7" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="n"/>
+      <c r="B180" s="7" t="n"/>
+      <c r="C180" s="7" t="n"/>
+      <c r="D180" s="7" t="n"/>
+      <c r="E180" s="7" t="n"/>
+      <c r="F180" s="7" t="n"/>
+      <c r="G180" s="7" t="n"/>
+      <c r="H180" s="7">
+        <f>IF(E180="Consumo",IFERROR(D180*VLOOKUP(VLOOKUP(C180,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C180,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F180*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G180*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I180" s="7" t="n"/>
+      <c r="J180" s="7" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="n"/>
+      <c r="B181" s="7" t="n"/>
+      <c r="C181" s="7" t="n"/>
+      <c r="D181" s="7" t="n"/>
+      <c r="E181" s="7" t="n"/>
+      <c r="F181" s="7" t="n"/>
+      <c r="G181" s="7" t="n"/>
+      <c r="H181" s="7">
+        <f>IF(E181="Consumo",IFERROR(D181*VLOOKUP(VLOOKUP(C181,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C181,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F181*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G181*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I181" s="7" t="n"/>
+      <c r="J181" s="7" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="n"/>
+      <c r="B182" s="7" t="n"/>
+      <c r="C182" s="7" t="n"/>
+      <c r="D182" s="7" t="n"/>
+      <c r="E182" s="7" t="n"/>
+      <c r="F182" s="7" t="n"/>
+      <c r="G182" s="7" t="n"/>
+      <c r="H182" s="7">
+        <f>IF(E182="Consumo",IFERROR(D182*VLOOKUP(VLOOKUP(C182,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C182,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F182*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G182*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I182" s="7" t="n"/>
+      <c r="J182" s="7" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="n"/>
+      <c r="B183" s="7" t="n"/>
+      <c r="C183" s="7" t="n"/>
+      <c r="D183" s="7" t="n"/>
+      <c r="E183" s="7" t="n"/>
+      <c r="F183" s="7" t="n"/>
+      <c r="G183" s="7" t="n"/>
+      <c r="H183" s="7">
+        <f>IF(E183="Consumo",IFERROR(D183*VLOOKUP(VLOOKUP(C183,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C183,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F183*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G183*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="7" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="n"/>
+      <c r="B184" s="7" t="n"/>
+      <c r="C184" s="7" t="n"/>
+      <c r="D184" s="7" t="n"/>
+      <c r="E184" s="7" t="n"/>
+      <c r="F184" s="7" t="n"/>
+      <c r="G184" s="7" t="n"/>
+      <c r="H184" s="7">
+        <f>IF(E184="Consumo",IFERROR(D184*VLOOKUP(VLOOKUP(C184,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C184,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F184*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G184*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I184" s="7" t="n"/>
+      <c r="J184" s="7" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="n"/>
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="7" t="n"/>
+      <c r="D185" s="7" t="n"/>
+      <c r="E185" s="7" t="n"/>
+      <c r="F185" s="7" t="n"/>
+      <c r="G185" s="7" t="n"/>
+      <c r="H185" s="7">
+        <f>IF(E185="Consumo",IFERROR(D185*VLOOKUP(VLOOKUP(C185,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C185,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F185*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G185*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I185" s="7" t="n"/>
+      <c r="J185" s="7" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="n"/>
+      <c r="B186" s="7" t="n"/>
+      <c r="C186" s="7" t="n"/>
+      <c r="D186" s="7" t="n"/>
+      <c r="E186" s="7" t="n"/>
+      <c r="F186" s="7" t="n"/>
+      <c r="G186" s="7" t="n"/>
+      <c r="H186" s="7">
+        <f>IF(E186="Consumo",IFERROR(D186*VLOOKUP(VLOOKUP(C186,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C186,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F186*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G186*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I186" s="7" t="n"/>
+      <c r="J186" s="7" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="n"/>
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="7" t="n"/>
+      <c r="D187" s="7" t="n"/>
+      <c r="E187" s="7" t="n"/>
+      <c r="F187" s="7" t="n"/>
+      <c r="G187" s="7" t="n"/>
+      <c r="H187" s="7">
+        <f>IF(E187="Consumo",IFERROR(D187*VLOOKUP(VLOOKUP(C187,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C187,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F187*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G187*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I187" s="7" t="n"/>
+      <c r="J187" s="7" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="n"/>
+      <c r="B188" s="7" t="n"/>
+      <c r="C188" s="7" t="n"/>
+      <c r="D188" s="7" t="n"/>
+      <c r="E188" s="7" t="n"/>
+      <c r="F188" s="7" t="n"/>
+      <c r="G188" s="7" t="n"/>
+      <c r="H188" s="7">
+        <f>IF(E188="Consumo",IFERROR(D188*VLOOKUP(VLOOKUP(C188,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C188,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F188*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G188*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I188" s="7" t="n"/>
+      <c r="J188" s="7" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="n"/>
+      <c r="B189" s="7" t="n"/>
+      <c r="C189" s="7" t="n"/>
+      <c r="D189" s="7" t="n"/>
+      <c r="E189" s="7" t="n"/>
+      <c r="F189" s="7" t="n"/>
+      <c r="G189" s="7" t="n"/>
+      <c r="H189" s="7">
+        <f>IF(E189="Consumo",IFERROR(D189*VLOOKUP(VLOOKUP(C189,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C189,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F189*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G189*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I189" s="7" t="n"/>
+      <c r="J189" s="7" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="n"/>
+      <c r="B190" s="7" t="n"/>
+      <c r="C190" s="7" t="n"/>
+      <c r="D190" s="7" t="n"/>
+      <c r="E190" s="7" t="n"/>
+      <c r="F190" s="7" t="n"/>
+      <c r="G190" s="7" t="n"/>
+      <c r="H190" s="7">
+        <f>IF(E190="Consumo",IFERROR(D190*VLOOKUP(VLOOKUP(C190,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C190,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F190*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G190*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I190" s="7" t="n"/>
+      <c r="J190" s="7" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="n"/>
+      <c r="B191" s="7" t="n"/>
+      <c r="C191" s="7" t="n"/>
+      <c r="D191" s="7" t="n"/>
+      <c r="E191" s="7" t="n"/>
+      <c r="F191" s="7" t="n"/>
+      <c r="G191" s="7" t="n"/>
+      <c r="H191" s="7">
+        <f>IF(E191="Consumo",IFERROR(D191*VLOOKUP(VLOOKUP(C191,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C191,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F191*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G191*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I191" s="7" t="n"/>
+      <c r="J191" s="7" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="n"/>
+      <c r="B192" s="7" t="n"/>
+      <c r="C192" s="7" t="n"/>
+      <c r="D192" s="7" t="n"/>
+      <c r="E192" s="7" t="n"/>
+      <c r="F192" s="7" t="n"/>
+      <c r="G192" s="7" t="n"/>
+      <c r="H192" s="7">
+        <f>IF(E192="Consumo",IFERROR(D192*VLOOKUP(VLOOKUP(C192,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C192,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F192*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G192*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I192" s="7" t="n"/>
+      <c r="J192" s="7" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="n"/>
+      <c r="B193" s="7" t="n"/>
+      <c r="C193" s="7" t="n"/>
+      <c r="D193" s="7" t="n"/>
+      <c r="E193" s="7" t="n"/>
+      <c r="F193" s="7" t="n"/>
+      <c r="G193" s="7" t="n"/>
+      <c r="H193" s="7">
+        <f>IF(E193="Consumo",IFERROR(D193*VLOOKUP(VLOOKUP(C193,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C193,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F193*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G193*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I193" s="7" t="n"/>
+      <c r="J193" s="7" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="n"/>
+      <c r="B194" s="7" t="n"/>
+      <c r="C194" s="7" t="n"/>
+      <c r="D194" s="7" t="n"/>
+      <c r="E194" s="7" t="n"/>
+      <c r="F194" s="7" t="n"/>
+      <c r="G194" s="7" t="n"/>
+      <c r="H194" s="7">
+        <f>IF(E194="Consumo",IFERROR(D194*VLOOKUP(VLOOKUP(C194,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C194,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F194*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G194*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I194" s="7" t="n"/>
+      <c r="J194" s="7" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="n"/>
+      <c r="B195" s="7" t="n"/>
+      <c r="C195" s="7" t="n"/>
+      <c r="D195" s="7" t="n"/>
+      <c r="E195" s="7" t="n"/>
+      <c r="F195" s="7" t="n"/>
+      <c r="G195" s="7" t="n"/>
+      <c r="H195" s="7">
+        <f>IF(E195="Consumo",IFERROR(D195*VLOOKUP(VLOOKUP(C195,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C195,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F195*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G195*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I195" s="7" t="n"/>
+      <c r="J195" s="7" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="n"/>
+      <c r="B196" s="7" t="n"/>
+      <c r="C196" s="7" t="n"/>
+      <c r="D196" s="7" t="n"/>
+      <c r="E196" s="7" t="n"/>
+      <c r="F196" s="7" t="n"/>
+      <c r="G196" s="7" t="n"/>
+      <c r="H196" s="7">
+        <f>IF(E196="Consumo",IFERROR(D196*VLOOKUP(VLOOKUP(C196,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C196,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F196*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G196*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I196" s="7" t="n"/>
+      <c r="J196" s="7" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="n"/>
+      <c r="B197" s="7" t="n"/>
+      <c r="C197" s="7" t="n"/>
+      <c r="D197" s="7" t="n"/>
+      <c r="E197" s="7" t="n"/>
+      <c r="F197" s="7" t="n"/>
+      <c r="G197" s="7" t="n"/>
+      <c r="H197" s="7">
+        <f>IF(E197="Consumo",IFERROR(D197*VLOOKUP(VLOOKUP(C197,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C197,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F197*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G197*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I197" s="7" t="n"/>
+      <c r="J197" s="7" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="n"/>
+      <c r="B198" s="7" t="n"/>
+      <c r="C198" s="7" t="n"/>
+      <c r="D198" s="7" t="n"/>
+      <c r="E198" s="7" t="n"/>
+      <c r="F198" s="7" t="n"/>
+      <c r="G198" s="7" t="n"/>
+      <c r="H198" s="7">
+        <f>IF(E198="Consumo",IFERROR(D198*VLOOKUP(VLOOKUP(C198,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C198,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F198*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G198*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="7" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="n"/>
+      <c r="B199" s="7" t="n"/>
+      <c r="C199" s="7" t="n"/>
+      <c r="D199" s="7" t="n"/>
+      <c r="E199" s="7" t="n"/>
+      <c r="F199" s="7" t="n"/>
+      <c r="G199" s="7" t="n"/>
+      <c r="H199" s="7">
+        <f>IF(E199="Consumo",IFERROR(D199*VLOOKUP(VLOOKUP(C199,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C199,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F199*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G199*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I199" s="7" t="n"/>
+      <c r="J199" s="7" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="n"/>
+      <c r="B200" s="7" t="n"/>
+      <c r="C200" s="7" t="n"/>
+      <c r="D200" s="7" t="n"/>
+      <c r="E200" s="7" t="n"/>
+      <c r="F200" s="7" t="n"/>
+      <c r="G200" s="7" t="n"/>
+      <c r="H200" s="7">
+        <f>IF(E200="Consumo",IFERROR(D200*VLOOKUP(VLOOKUP(C200,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C200,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F200*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G200*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I200" s="7" t="n"/>
+      <c r="J200" s="7" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="n"/>
+      <c r="B201" s="7" t="n"/>
+      <c r="C201" s="7" t="n"/>
+      <c r="D201" s="7" t="n"/>
+      <c r="E201" s="7" t="n"/>
+      <c r="F201" s="7" t="n"/>
+      <c r="G201" s="7" t="n"/>
+      <c r="H201" s="7">
+        <f>IF(E201="Consumo",IFERROR(D201*VLOOKUP(VLOOKUP(C201,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C201,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F201*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G201*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I201" s="7" t="n"/>
+      <c r="J201" s="7" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="n"/>
+      <c r="B202" s="7" t="n"/>
+      <c r="C202" s="7" t="n"/>
+      <c r="D202" s="7" t="n"/>
+      <c r="E202" s="7" t="n"/>
+      <c r="F202" s="7" t="n"/>
+      <c r="G202" s="7" t="n"/>
+      <c r="H202" s="7">
+        <f>IF(E202="Consumo",IFERROR(D202*VLOOKUP(VLOOKUP(C202,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C202,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F202*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G202*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I202" s="7" t="n"/>
+      <c r="J202" s="7" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="n"/>
+      <c r="B203" s="7" t="n"/>
+      <c r="C203" s="7" t="n"/>
+      <c r="D203" s="7" t="n"/>
+      <c r="E203" s="7" t="n"/>
+      <c r="F203" s="7" t="n"/>
+      <c r="G203" s="7" t="n"/>
+      <c r="H203" s="7">
+        <f>IF(E203="Consumo",IFERROR(D203*VLOOKUP(VLOOKUP(C203,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C203,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F203*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G203*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I203" s="7" t="n"/>
+      <c r="J203" s="7" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="n"/>
+      <c r="B204" s="7" t="n"/>
+      <c r="C204" s="7" t="n"/>
+      <c r="D204" s="7" t="n"/>
+      <c r="E204" s="7" t="n"/>
+      <c r="F204" s="7" t="n"/>
+      <c r="G204" s="7" t="n"/>
+      <c r="H204" s="7">
+        <f>IF(E204="Consumo",IFERROR(D204*VLOOKUP(VLOOKUP(C204,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C204,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F204*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G204*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I204" s="7" t="n"/>
+      <c r="J204" s="7" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="n"/>
+      <c r="B205" s="7" t="n"/>
+      <c r="C205" s="7" t="n"/>
+      <c r="D205" s="7" t="n"/>
+      <c r="E205" s="7" t="n"/>
+      <c r="F205" s="7" t="n"/>
+      <c r="G205" s="7" t="n"/>
+      <c r="H205" s="7">
+        <f>IF(E205="Consumo",IFERROR(D205*VLOOKUP(VLOOKUP(C205,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C205,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F205*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G205*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I205" s="7" t="n"/>
+      <c r="J205" s="7" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="n"/>
+      <c r="B206" s="7" t="n"/>
+      <c r="C206" s="7" t="n"/>
+      <c r="D206" s="7" t="n"/>
+      <c r="E206" s="7" t="n"/>
+      <c r="F206" s="7" t="n"/>
+      <c r="G206" s="7" t="n"/>
+      <c r="H206" s="7">
+        <f>IF(E206="Consumo",IFERROR(D206*VLOOKUP(VLOOKUP(C206,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C206,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F206*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G206*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I206" s="7" t="n"/>
+      <c r="J206" s="7" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="n"/>
+      <c r="B207" s="7" t="n"/>
+      <c r="C207" s="7" t="n"/>
+      <c r="D207" s="7" t="n"/>
+      <c r="E207" s="7" t="n"/>
+      <c r="F207" s="7" t="n"/>
+      <c r="G207" s="7" t="n"/>
+      <c r="H207" s="7">
+        <f>IF(E207="Consumo",IFERROR(D207*VLOOKUP(VLOOKUP(C207,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C207,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F207*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G207*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I207" s="7" t="n"/>
+      <c r="J207" s="7" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="n"/>
+      <c r="B208" s="7" t="n"/>
+      <c r="C208" s="7" t="n"/>
+      <c r="D208" s="7" t="n"/>
+      <c r="E208" s="7" t="n"/>
+      <c r="F208" s="7" t="n"/>
+      <c r="G208" s="7" t="n"/>
+      <c r="H208" s="7">
+        <f>IF(E208="Consumo",IFERROR(D208*VLOOKUP(VLOOKUP(C208,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C208,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F208*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G208*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I208" s="7" t="n"/>
+      <c r="J208" s="7" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="n"/>
+      <c r="B209" s="7" t="n"/>
+      <c r="C209" s="7" t="n"/>
+      <c r="D209" s="7" t="n"/>
+      <c r="E209" s="7" t="n"/>
+      <c r="F209" s="7" t="n"/>
+      <c r="G209" s="7" t="n"/>
+      <c r="H209" s="7">
+        <f>IF(E209="Consumo",IFERROR(D209*VLOOKUP(VLOOKUP(C209,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C209,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F209*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G209*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I209" s="7" t="n"/>
+      <c r="J209" s="7" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="n"/>
+      <c r="B210" s="7" t="n"/>
+      <c r="C210" s="7" t="n"/>
+      <c r="D210" s="7" t="n"/>
+      <c r="E210" s="7" t="n"/>
+      <c r="F210" s="7" t="n"/>
+      <c r="G210" s="7" t="n"/>
+      <c r="H210" s="7">
+        <f>IF(E210="Consumo",IFERROR(D210*VLOOKUP(VLOOKUP(C210,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C210,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F210*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G210*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I210" s="7" t="n"/>
+      <c r="J210" s="7" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="n"/>
+      <c r="B211" s="7" t="n"/>
+      <c r="C211" s="7" t="n"/>
+      <c r="D211" s="7" t="n"/>
+      <c r="E211" s="7" t="n"/>
+      <c r="F211" s="7" t="n"/>
+      <c r="G211" s="7" t="n"/>
+      <c r="H211" s="7">
+        <f>IF(E211="Consumo",IFERROR(D211*VLOOKUP(VLOOKUP(C211,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C211,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F211*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G211*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I211" s="7" t="n"/>
+      <c r="J211" s="7" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="n"/>
+      <c r="B212" s="7" t="n"/>
+      <c r="C212" s="7" t="n"/>
+      <c r="D212" s="7" t="n"/>
+      <c r="E212" s="7" t="n"/>
+      <c r="F212" s="7" t="n"/>
+      <c r="G212" s="7" t="n"/>
+      <c r="H212" s="7">
+        <f>IF(E212="Consumo",IFERROR(D212*VLOOKUP(VLOOKUP(C212,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C212,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F212*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G212*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I212" s="7" t="n"/>
+      <c r="J212" s="7" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="n"/>
+      <c r="B213" s="7" t="n"/>
+      <c r="C213" s="7" t="n"/>
+      <c r="D213" s="7" t="n"/>
+      <c r="E213" s="7" t="n"/>
+      <c r="F213" s="7" t="n"/>
+      <c r="G213" s="7" t="n"/>
+      <c r="H213" s="7">
+        <f>IF(E213="Consumo",IFERROR(D213*VLOOKUP(VLOOKUP(C213,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C213,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F213*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G213*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I213" s="7" t="n"/>
+      <c r="J213" s="7" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="n"/>
+      <c r="B214" s="7" t="n"/>
+      <c r="C214" s="7" t="n"/>
+      <c r="D214" s="7" t="n"/>
+      <c r="E214" s="7" t="n"/>
+      <c r="F214" s="7" t="n"/>
+      <c r="G214" s="7" t="n"/>
+      <c r="H214" s="7">
+        <f>IF(E214="Consumo",IFERROR(D214*VLOOKUP(VLOOKUP(C214,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C214,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F214*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G214*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I214" s="7" t="n"/>
+      <c r="J214" s="7" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="n"/>
+      <c r="B215" s="7" t="n"/>
+      <c r="C215" s="7" t="n"/>
+      <c r="D215" s="7" t="n"/>
+      <c r="E215" s="7" t="n"/>
+      <c r="F215" s="7" t="n"/>
+      <c r="G215" s="7" t="n"/>
+      <c r="H215" s="7">
+        <f>IF(E215="Consumo",IFERROR(D215*VLOOKUP(VLOOKUP(C215,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C215,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F215*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G215*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I215" s="7" t="n"/>
+      <c r="J215" s="7" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="n"/>
+      <c r="B216" s="7" t="n"/>
+      <c r="C216" s="7" t="n"/>
+      <c r="D216" s="7" t="n"/>
+      <c r="E216" s="7" t="n"/>
+      <c r="F216" s="7" t="n"/>
+      <c r="G216" s="7" t="n"/>
+      <c r="H216" s="7">
+        <f>IF(E216="Consumo",IFERROR(D216*VLOOKUP(VLOOKUP(C216,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C216,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F216*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G216*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I216" s="7" t="n"/>
+      <c r="J216" s="7" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="n"/>
+      <c r="B217" s="7" t="n"/>
+      <c r="C217" s="7" t="n"/>
+      <c r="D217" s="7" t="n"/>
+      <c r="E217" s="7" t="n"/>
+      <c r="F217" s="7" t="n"/>
+      <c r="G217" s="7" t="n"/>
+      <c r="H217" s="7">
+        <f>IF(E217="Consumo",IFERROR(D217*VLOOKUP(VLOOKUP(C217,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C217,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F217*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G217*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I217" s="7" t="n"/>
+      <c r="J217" s="7" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="n"/>
+      <c r="B218" s="7" t="n"/>
+      <c r="C218" s="7" t="n"/>
+      <c r="D218" s="7" t="n"/>
+      <c r="E218" s="7" t="n"/>
+      <c r="F218" s="7" t="n"/>
+      <c r="G218" s="7" t="n"/>
+      <c r="H218" s="7">
+        <f>IF(E218="Consumo",IFERROR(D218*VLOOKUP(VLOOKUP(C218,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C218,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F218*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G218*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I218" s="7" t="n"/>
+      <c r="J218" s="7" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="n"/>
+      <c r="B219" s="7" t="n"/>
+      <c r="C219" s="7" t="n"/>
+      <c r="D219" s="7" t="n"/>
+      <c r="E219" s="7" t="n"/>
+      <c r="F219" s="7" t="n"/>
+      <c r="G219" s="7" t="n"/>
+      <c r="H219" s="7">
+        <f>IF(E219="Consumo",IFERROR(D219*VLOOKUP(VLOOKUP(C219,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C219,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F219*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G219*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I219" s="7" t="n"/>
+      <c r="J219" s="7" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="n"/>
+      <c r="B220" s="7" t="n"/>
+      <c r="C220" s="7" t="n"/>
+      <c r="D220" s="7" t="n"/>
+      <c r="E220" s="7" t="n"/>
+      <c r="F220" s="7" t="n"/>
+      <c r="G220" s="7" t="n"/>
+      <c r="H220" s="7">
+        <f>IF(E220="Consumo",IFERROR(D220*VLOOKUP(VLOOKUP(C220,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C220,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F220*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G220*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I220" s="7" t="n"/>
+      <c r="J220" s="7" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="n"/>
+      <c r="B221" s="7" t="n"/>
+      <c r="C221" s="7" t="n"/>
+      <c r="D221" s="7" t="n"/>
+      <c r="E221" s="7" t="n"/>
+      <c r="F221" s="7" t="n"/>
+      <c r="G221" s="7" t="n"/>
+      <c r="H221" s="7">
+        <f>IF(E221="Consumo",IFERROR(D221*VLOOKUP(VLOOKUP(C221,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C221,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F221*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G221*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I221" s="7" t="n"/>
+      <c r="J221" s="7" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="n"/>
+      <c r="B222" s="7" t="n"/>
+      <c r="C222" s="7" t="n"/>
+      <c r="D222" s="7" t="n"/>
+      <c r="E222" s="7" t="n"/>
+      <c r="F222" s="7" t="n"/>
+      <c r="G222" s="7" t="n"/>
+      <c r="H222" s="7">
+        <f>IF(E222="Consumo",IFERROR(D222*VLOOKUP(VLOOKUP(C222,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C222,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F222*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G222*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I222" s="7" t="n"/>
+      <c r="J222" s="7" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="n"/>
+      <c r="B223" s="7" t="n"/>
+      <c r="C223" s="7" t="n"/>
+      <c r="D223" s="7" t="n"/>
+      <c r="E223" s="7" t="n"/>
+      <c r="F223" s="7" t="n"/>
+      <c r="G223" s="7" t="n"/>
+      <c r="H223" s="7">
+        <f>IF(E223="Consumo",IFERROR(D223*VLOOKUP(VLOOKUP(C223,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C223,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F223*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G223*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I223" s="7" t="n"/>
+      <c r="J223" s="7" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="n"/>
+      <c r="B224" s="7" t="n"/>
+      <c r="C224" s="7" t="n"/>
+      <c r="D224" s="7" t="n"/>
+      <c r="E224" s="7" t="n"/>
+      <c r="F224" s="7" t="n"/>
+      <c r="G224" s="7" t="n"/>
+      <c r="H224" s="7">
+        <f>IF(E224="Consumo",IFERROR(D224*VLOOKUP(VLOOKUP(C224,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C224,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F224*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G224*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I224" s="7" t="n"/>
+      <c r="J224" s="7" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="7" t="n"/>
+      <c r="B225" s="7" t="n"/>
+      <c r="C225" s="7" t="n"/>
+      <c r="D225" s="7" t="n"/>
+      <c r="E225" s="7" t="n"/>
+      <c r="F225" s="7" t="n"/>
+      <c r="G225" s="7" t="n"/>
+      <c r="H225" s="7">
+        <f>IF(E225="Consumo",IFERROR(D225*VLOOKUP(VLOOKUP(C225,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C225,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F225*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G225*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I225" s="7" t="n"/>
+      <c r="J225" s="7" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="n"/>
+      <c r="B226" s="7" t="n"/>
+      <c r="C226" s="7" t="n"/>
+      <c r="D226" s="7" t="n"/>
+      <c r="E226" s="7" t="n"/>
+      <c r="F226" s="7" t="n"/>
+      <c r="G226" s="7" t="n"/>
+      <c r="H226" s="7">
+        <f>IF(E226="Consumo",IFERROR(D226*VLOOKUP(VLOOKUP(C226,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C226,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F226*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G226*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I226" s="7" t="n"/>
+      <c r="J226" s="7" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="n"/>
+      <c r="B227" s="7" t="n"/>
+      <c r="C227" s="7" t="n"/>
+      <c r="D227" s="7" t="n"/>
+      <c r="E227" s="7" t="n"/>
+      <c r="F227" s="7" t="n"/>
+      <c r="G227" s="7" t="n"/>
+      <c r="H227" s="7">
+        <f>IF(E227="Consumo",IFERROR(D227*VLOOKUP(VLOOKUP(C227,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C227,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F227*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G227*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I227" s="7" t="n"/>
+      <c r="J227" s="7" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="7" t="n"/>
+      <c r="B228" s="7" t="n"/>
+      <c r="C228" s="7" t="n"/>
+      <c r="D228" s="7" t="n"/>
+      <c r="E228" s="7" t="n"/>
+      <c r="F228" s="7" t="n"/>
+      <c r="G228" s="7" t="n"/>
+      <c r="H228" s="7">
+        <f>IF(E228="Consumo",IFERROR(D228*VLOOKUP(VLOOKUP(C228,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C228,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F228*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G228*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I228" s="7" t="n"/>
+      <c r="J228" s="7" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="n"/>
+      <c r="B229" s="7" t="n"/>
+      <c r="C229" s="7" t="n"/>
+      <c r="D229" s="7" t="n"/>
+      <c r="E229" s="7" t="n"/>
+      <c r="F229" s="7" t="n"/>
+      <c r="G229" s="7" t="n"/>
+      <c r="H229" s="7">
+        <f>IF(E229="Consumo",IFERROR(D229*VLOOKUP(VLOOKUP(C229,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C229,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F229*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G229*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I229" s="7" t="n"/>
+      <c r="J229" s="7" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="n"/>
+      <c r="B230" s="7" t="n"/>
+      <c r="C230" s="7" t="n"/>
+      <c r="D230" s="7" t="n"/>
+      <c r="E230" s="7" t="n"/>
+      <c r="F230" s="7" t="n"/>
+      <c r="G230" s="7" t="n"/>
+      <c r="H230" s="7">
+        <f>IF(E230="Consumo",IFERROR(D230*VLOOKUP(VLOOKUP(C230,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C230,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F230*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G230*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I230" s="7" t="n"/>
+      <c r="J230" s="7" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="n"/>
+      <c r="B231" s="7" t="n"/>
+      <c r="C231" s="7" t="n"/>
+      <c r="D231" s="7" t="n"/>
+      <c r="E231" s="7" t="n"/>
+      <c r="F231" s="7" t="n"/>
+      <c r="G231" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H151" s="13">
-        <f>SUM(H2:H150)</f>
+      <c r="H231" s="7">
+        <f>SUM(H2:H231)</f>
+        <v/>
+      </c>
+      <c r="I231" s="7" t="n"/>
+      <c r="J231" s="7" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="n"/>
+      <c r="B232" s="7" t="n"/>
+      <c r="C232" s="7" t="n"/>
+      <c r="D232" s="7" t="n"/>
+      <c r="E232" s="7" t="n"/>
+      <c r="F232" s="7" t="n"/>
+      <c r="G232" s="7" t="n"/>
+      <c r="H232" s="7">
+        <f>IF(E232="Consumo",IFERROR(D232*VLOOKUP(VLOOKUP(C232,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C232,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F232*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G232*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I232" s="7" t="n"/>
+      <c r="J232" s="7" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="n"/>
+      <c r="B233" s="7" t="n"/>
+      <c r="C233" s="7" t="n"/>
+      <c r="D233" s="7" t="n"/>
+      <c r="E233" s="7" t="n"/>
+      <c r="F233" s="7" t="n"/>
+      <c r="G233" s="7" t="n"/>
+      <c r="H233" s="7">
+        <f>IF(E233="Consumo",IFERROR(D233*VLOOKUP(VLOOKUP(C233,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C233,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F233*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G233*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I233" s="7" t="n"/>
+      <c r="J233" s="7" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="n"/>
+      <c r="B234" s="7" t="n"/>
+      <c r="C234" s="7" t="n"/>
+      <c r="D234" s="7" t="n"/>
+      <c r="E234" s="7" t="n"/>
+      <c r="F234" s="7" t="n"/>
+      <c r="G234" s="7" t="n"/>
+      <c r="H234" s="7">
+        <f>IF(E234="Consumo",IFERROR(D234*VLOOKUP(VLOOKUP(C234,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C234,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F234*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G234*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I234" s="7" t="n"/>
+      <c r="J234" s="7" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="n"/>
+      <c r="B235" s="7" t="n"/>
+      <c r="C235" s="7" t="n"/>
+      <c r="D235" s="7" t="n"/>
+      <c r="E235" s="7" t="n"/>
+      <c r="F235" s="7" t="n"/>
+      <c r="G235" s="7" t="n"/>
+      <c r="H235" s="7">
+        <f>IF(E235="Consumo",IFERROR(D235*VLOOKUP(VLOOKUP(C235,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C235,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F235*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G235*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I235" s="7" t="n"/>
+      <c r="J235" s="7" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="n"/>
+      <c r="B236" s="7" t="n"/>
+      <c r="C236" s="7" t="n"/>
+      <c r="D236" s="7" t="n"/>
+      <c r="E236" s="7" t="n"/>
+      <c r="F236" s="7" t="n"/>
+      <c r="G236" s="7" t="n"/>
+      <c r="H236" s="7">
+        <f>IF(E236="Consumo",IFERROR(D236*VLOOKUP(VLOOKUP(C236,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C236,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F236*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G236*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I236" s="7" t="n"/>
+      <c r="J236" s="7" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="n"/>
+      <c r="B237" s="7" t="n"/>
+      <c r="C237" s="7" t="n"/>
+      <c r="D237" s="7" t="n"/>
+      <c r="E237" s="7" t="n"/>
+      <c r="F237" s="7" t="n"/>
+      <c r="G237" s="7" t="n"/>
+      <c r="H237" s="7">
+        <f>IF(E237="Consumo",IFERROR(D237*VLOOKUP(VLOOKUP(C237,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C237,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F237*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G237*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I237" s="7" t="n"/>
+      <c r="J237" s="7" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="7" t="n"/>
+      <c r="B238" s="7" t="n"/>
+      <c r="C238" s="7" t="n"/>
+      <c r="D238" s="7" t="n"/>
+      <c r="E238" s="7" t="n"/>
+      <c r="F238" s="7" t="n"/>
+      <c r="G238" s="7" t="n"/>
+      <c r="H238" s="7">
+        <f>IF(E238="Consumo",IFERROR(D238*VLOOKUP(VLOOKUP(C238,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C238,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F238*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G238*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I238" s="7" t="n"/>
+      <c r="J238" s="7" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="n"/>
+      <c r="B239" s="7" t="n"/>
+      <c r="C239" s="7" t="n"/>
+      <c r="D239" s="7" t="n"/>
+      <c r="E239" s="7" t="n"/>
+      <c r="F239" s="7" t="n"/>
+      <c r="G239" s="7" t="n"/>
+      <c r="H239" s="7">
+        <f>IF(E239="Consumo",IFERROR(D239*VLOOKUP(VLOOKUP(C239,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C239,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F239*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G239*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I239" s="7" t="n"/>
+      <c r="J239" s="7" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="n"/>
+      <c r="B240" s="7" t="n"/>
+      <c r="C240" s="7" t="n"/>
+      <c r="D240" s="7" t="n"/>
+      <c r="E240" s="7" t="n"/>
+      <c r="F240" s="7" t="n"/>
+      <c r="G240" s="7" t="n"/>
+      <c r="H240" s="7">
+        <f>IF(E240="Consumo",IFERROR(D240*VLOOKUP(VLOOKUP(C240,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C240,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F240*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G240*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I240" s="7" t="n"/>
+      <c r="J240" s="7" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="n"/>
+      <c r="B241" s="7" t="n"/>
+      <c r="C241" s="7" t="n"/>
+      <c r="D241" s="7" t="n"/>
+      <c r="E241" s="7" t="n"/>
+      <c r="F241" s="7" t="n"/>
+      <c r="G241" s="7" t="n"/>
+      <c r="H241" s="7">
+        <f>IF(E241="Consumo",IFERROR(D241*VLOOKUP(VLOOKUP(C241,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C241,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F241*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G241*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I241" s="7" t="n"/>
+      <c r="J241" s="7" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="7" t="n"/>
+      <c r="B242" s="7" t="n"/>
+      <c r="C242" s="7" t="n"/>
+      <c r="D242" s="7" t="n"/>
+      <c r="E242" s="7" t="n"/>
+      <c r="F242" s="7" t="n"/>
+      <c r="G242" s="7" t="n"/>
+      <c r="H242" s="7">
+        <f>IF(E242="Consumo",IFERROR(D242*VLOOKUP(VLOOKUP(C242,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C242,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F242*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G242*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I242" s="7" t="n"/>
+      <c r="J242" s="7" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="7" t="n"/>
+      <c r="B243" s="7" t="n"/>
+      <c r="C243" s="7" t="n"/>
+      <c r="D243" s="7" t="n"/>
+      <c r="E243" s="7" t="n"/>
+      <c r="F243" s="7" t="n"/>
+      <c r="G243" s="7" t="n"/>
+      <c r="H243" s="7">
+        <f>IF(E243="Consumo",IFERROR(D243*VLOOKUP(VLOOKUP(C243,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C243,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F243*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G243*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I243" s="7" t="n"/>
+      <c r="J243" s="7" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="7" t="n"/>
+      <c r="B244" s="7" t="n"/>
+      <c r="C244" s="7" t="n"/>
+      <c r="D244" s="7" t="n"/>
+      <c r="E244" s="7" t="n"/>
+      <c r="F244" s="7" t="n"/>
+      <c r="G244" s="7" t="n"/>
+      <c r="H244" s="7">
+        <f>IF(E244="Consumo",IFERROR(D244*VLOOKUP(VLOOKUP(C244,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C244,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F244*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G244*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I244" s="7" t="n"/>
+      <c r="J244" s="7" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="7" t="n"/>
+      <c r="B245" s="7" t="n"/>
+      <c r="C245" s="7" t="n"/>
+      <c r="D245" s="7" t="n"/>
+      <c r="E245" s="7" t="n"/>
+      <c r="F245" s="7" t="n"/>
+      <c r="G245" s="7" t="n"/>
+      <c r="H245" s="7">
+        <f>IF(E245="Consumo",IFERROR(D245*VLOOKUP(VLOOKUP(C245,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C245,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F245*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G245*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I245" s="7" t="n"/>
+      <c r="J245" s="7" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="n"/>
+      <c r="B246" s="7" t="n"/>
+      <c r="C246" s="7" t="n"/>
+      <c r="D246" s="7" t="n"/>
+      <c r="E246" s="7" t="n"/>
+      <c r="F246" s="7" t="n"/>
+      <c r="G246" s="7" t="n"/>
+      <c r="H246" s="7">
+        <f>IF(E246="Consumo",IFERROR(D246*VLOOKUP(VLOOKUP(C246,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C246,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F246*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G246*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I246" s="7" t="n"/>
+      <c r="J246" s="7" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="7" t="n"/>
+      <c r="B247" s="7" t="n"/>
+      <c r="C247" s="7" t="n"/>
+      <c r="D247" s="7" t="n"/>
+      <c r="E247" s="7" t="n"/>
+      <c r="F247" s="7" t="n"/>
+      <c r="G247" s="7" t="n"/>
+      <c r="H247" s="7">
+        <f>IF(E247="Consumo",IFERROR(D247*VLOOKUP(VLOOKUP(C247,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C247,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F247*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G247*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I247" s="7" t="n"/>
+      <c r="J247" s="7" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="7" t="n"/>
+      <c r="B248" s="7" t="n"/>
+      <c r="C248" s="7" t="n"/>
+      <c r="D248" s="7" t="n"/>
+      <c r="E248" s="7" t="n"/>
+      <c r="F248" s="7" t="n"/>
+      <c r="G248" s="7" t="n"/>
+      <c r="H248" s="7">
+        <f>IF(E248="Consumo",IFERROR(D248*VLOOKUP(VLOOKUP(C248,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C248,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F248*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G248*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I248" s="7" t="n"/>
+      <c r="J248" s="7" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="7" t="n"/>
+      <c r="B249" s="7" t="n"/>
+      <c r="C249" s="7" t="n"/>
+      <c r="D249" s="7" t="n"/>
+      <c r="E249" s="7" t="n"/>
+      <c r="F249" s="7" t="n"/>
+      <c r="G249" s="7" t="n"/>
+      <c r="H249" s="7">
+        <f>IF(E249="Consumo",IFERROR(D249*VLOOKUP(VLOOKUP(C249,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C249,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F249*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G249*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I249" s="7" t="n"/>
+      <c r="J249" s="7" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="7" t="n"/>
+      <c r="B250" s="7" t="n"/>
+      <c r="C250" s="7" t="n"/>
+      <c r="D250" s="7" t="n"/>
+      <c r="E250" s="7" t="n"/>
+      <c r="F250" s="7" t="n"/>
+      <c r="G250" s="7" t="n"/>
+      <c r="H250" s="7">
+        <f>IF(E250="Consumo",IFERROR(D250*VLOOKUP(VLOOKUP(C250,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C250,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F250*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G250*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I250" s="7" t="n"/>
+      <c r="J250" s="7" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="7" t="n"/>
+      <c r="B251" s="7" t="n"/>
+      <c r="C251" s="7" t="n"/>
+      <c r="D251" s="7" t="n"/>
+      <c r="E251" s="7" t="n"/>
+      <c r="F251" s="7" t="n"/>
+      <c r="G251" s="7" t="n"/>
+      <c r="H251" s="7">
+        <f>IF(E251="Consumo",IFERROR(D251*VLOOKUP(VLOOKUP(C251,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C251,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F251*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G251*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I251" s="7" t="n"/>
+      <c r="J251" s="7" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="7" t="n"/>
+      <c r="B252" s="7" t="n"/>
+      <c r="C252" s="7" t="n"/>
+      <c r="D252" s="7" t="n"/>
+      <c r="E252" s="7" t="n"/>
+      <c r="F252" s="7" t="n"/>
+      <c r="G252" s="7" t="n"/>
+      <c r="H252" s="7">
+        <f>IF(E252="Consumo",IFERROR(D252*VLOOKUP(VLOOKUP(C252,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C252,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F252*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G252*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I252" s="7" t="n"/>
+      <c r="J252" s="7" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="7" t="n"/>
+      <c r="B253" s="7" t="n"/>
+      <c r="C253" s="7" t="n"/>
+      <c r="D253" s="7" t="n"/>
+      <c r="E253" s="7" t="n"/>
+      <c r="F253" s="7" t="n"/>
+      <c r="G253" s="7" t="n"/>
+      <c r="H253" s="7">
+        <f>IF(E253="Consumo",IFERROR(D253*VLOOKUP(VLOOKUP(C253,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C253,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F253*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G253*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I253" s="7" t="n"/>
+      <c r="J253" s="7" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="7" t="n"/>
+      <c r="B254" s="7" t="n"/>
+      <c r="C254" s="7" t="n"/>
+      <c r="D254" s="7" t="n"/>
+      <c r="E254" s="7" t="n"/>
+      <c r="F254" s="7" t="n"/>
+      <c r="G254" s="7" t="n"/>
+      <c r="H254" s="7">
+        <f>IF(E254="Consumo",IFERROR(D254*VLOOKUP(VLOOKUP(C254,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C254,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F254*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G254*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I254" s="7" t="n"/>
+      <c r="J254" s="7" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="7" t="n"/>
+      <c r="B255" s="7" t="n"/>
+      <c r="C255" s="7" t="n"/>
+      <c r="D255" s="7" t="n"/>
+      <c r="E255" s="7" t="n"/>
+      <c r="F255" s="7" t="n"/>
+      <c r="G255" s="7" t="n"/>
+      <c r="H255" s="7">
+        <f>IF(E255="Consumo",IFERROR(D255*VLOOKUP(VLOOKUP(C255,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C255,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F255*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G255*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I255" s="7" t="n"/>
+      <c r="J255" s="7" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="7" t="n"/>
+      <c r="B256" s="7" t="n"/>
+      <c r="C256" s="7" t="n"/>
+      <c r="D256" s="7" t="n"/>
+      <c r="E256" s="7" t="n"/>
+      <c r="F256" s="7" t="n"/>
+      <c r="G256" s="7" t="n"/>
+      <c r="H256" s="7">
+        <f>IF(E256="Consumo",IFERROR(D256*VLOOKUP(VLOOKUP(C256,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C256,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F256*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G256*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I256" s="7" t="n"/>
+      <c r="J256" s="7" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="7" t="n"/>
+      <c r="B257" s="7" t="n"/>
+      <c r="C257" s="7" t="n"/>
+      <c r="D257" s="7" t="n"/>
+      <c r="E257" s="7" t="n"/>
+      <c r="F257" s="7" t="n"/>
+      <c r="G257" s="7" t="n"/>
+      <c r="H257" s="7">
+        <f>IF(E257="Consumo",IFERROR(D257*VLOOKUP(VLOOKUP(C257,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C257,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F257*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G257*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I257" s="7" t="n"/>
+      <c r="J257" s="7" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="7" t="n"/>
+      <c r="B258" s="7" t="n"/>
+      <c r="C258" s="7" t="n"/>
+      <c r="D258" s="7" t="n"/>
+      <c r="E258" s="7" t="n"/>
+      <c r="F258" s="7" t="n"/>
+      <c r="G258" s="7" t="n"/>
+      <c r="H258" s="7">
+        <f>IF(E258="Consumo",IFERROR(D258*VLOOKUP(VLOOKUP(C258,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C258,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F258*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G258*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I258" s="7" t="n"/>
+      <c r="J258" s="7" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="7" t="n"/>
+      <c r="B259" s="7" t="n"/>
+      <c r="C259" s="7" t="n"/>
+      <c r="D259" s="7" t="n"/>
+      <c r="E259" s="7" t="n"/>
+      <c r="F259" s="7" t="n"/>
+      <c r="G259" s="7" t="n"/>
+      <c r="H259" s="7">
+        <f>IF(E259="Consumo",IFERROR(D259*VLOOKUP(VLOOKUP(C259,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C259,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F259*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G259*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I259" s="7" t="n"/>
+      <c r="J259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="7" t="n"/>
+      <c r="B260" s="7" t="n"/>
+      <c r="C260" s="7" t="n"/>
+      <c r="D260" s="7" t="n"/>
+      <c r="E260" s="7" t="n"/>
+      <c r="F260" s="7" t="n"/>
+      <c r="G260" s="7" t="n"/>
+      <c r="H260" s="7">
+        <f>IF(E260="Consumo",IFERROR(D260*VLOOKUP(VLOOKUP(C260,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C260,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F260*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G260*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I260" s="7" t="n"/>
+      <c r="J260" s="7" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="7" t="n"/>
+      <c r="B261" s="7" t="n"/>
+      <c r="C261" s="7" t="n"/>
+      <c r="D261" s="7" t="n"/>
+      <c r="E261" s="7" t="n"/>
+      <c r="F261" s="7" t="n"/>
+      <c r="G261" s="7" t="n"/>
+      <c r="H261" s="7">
+        <f>IF(E261="Consumo",IFERROR(D261*VLOOKUP(VLOOKUP(C261,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C261,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F261*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G261*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I261" s="7" t="n"/>
+      <c r="J261" s="7" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="7" t="n"/>
+      <c r="B262" s="7" t="n"/>
+      <c r="C262" s="7" t="n"/>
+      <c r="D262" s="7" t="n"/>
+      <c r="E262" s="7" t="n"/>
+      <c r="F262" s="7" t="n"/>
+      <c r="G262" s="7" t="n"/>
+      <c r="H262" s="7">
+        <f>IF(E262="Consumo",IFERROR(D262*VLOOKUP(VLOOKUP(C262,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C262,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F262*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G262*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I262" s="7" t="n"/>
+      <c r="J262" s="7" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="7" t="n"/>
+      <c r="B263" s="7" t="n"/>
+      <c r="C263" s="7" t="n"/>
+      <c r="D263" s="7" t="n"/>
+      <c r="E263" s="7" t="n"/>
+      <c r="F263" s="7" t="n"/>
+      <c r="G263" s="7" t="n"/>
+      <c r="H263" s="7">
+        <f>IF(E263="Consumo",IFERROR(D263*VLOOKUP(VLOOKUP(C263,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C263,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F263*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G263*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I263" s="7" t="n"/>
+      <c r="J263" s="7" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="7" t="n"/>
+      <c r="B264" s="7" t="n"/>
+      <c r="C264" s="7" t="n"/>
+      <c r="D264" s="7" t="n"/>
+      <c r="E264" s="7" t="n"/>
+      <c r="F264" s="7" t="n"/>
+      <c r="G264" s="7" t="n"/>
+      <c r="H264" s="7">
+        <f>IF(E264="Consumo",IFERROR(D264*VLOOKUP(VLOOKUP(C264,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C264,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F264*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G264*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I264" s="7" t="n"/>
+      <c r="J264" s="7" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="7" t="n"/>
+      <c r="B265" s="7" t="n"/>
+      <c r="C265" s="7" t="n"/>
+      <c r="D265" s="7" t="n"/>
+      <c r="E265" s="7" t="n"/>
+      <c r="F265" s="7" t="n"/>
+      <c r="G265" s="7" t="n"/>
+      <c r="H265" s="7">
+        <f>IF(E265="Consumo",IFERROR(D265*VLOOKUP(VLOOKUP(C265,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C265,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F265*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G265*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I265" s="7" t="n"/>
+      <c r="J265" s="7" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="n"/>
+      <c r="B266" s="7" t="n"/>
+      <c r="C266" s="7" t="n"/>
+      <c r="D266" s="7" t="n"/>
+      <c r="E266" s="7" t="n"/>
+      <c r="F266" s="7" t="n"/>
+      <c r="G266" s="7" t="n"/>
+      <c r="H266" s="7">
+        <f>IF(E266="Consumo",IFERROR(D266*VLOOKUP(VLOOKUP(C266,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C266,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F266*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G266*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I266" s="7" t="n"/>
+      <c r="J266" s="7" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="7" t="n"/>
+      <c r="B267" s="7" t="n"/>
+      <c r="C267" s="7" t="n"/>
+      <c r="D267" s="7" t="n"/>
+      <c r="E267" s="7" t="n"/>
+      <c r="F267" s="7" t="n"/>
+      <c r="G267" s="7" t="n"/>
+      <c r="H267" s="7">
+        <f>IF(E267="Consumo",IFERROR(D267*VLOOKUP(VLOOKUP(C267,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C267,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F267*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G267*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I267" s="7" t="n"/>
+      <c r="J267" s="7" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="7" t="n"/>
+      <c r="B268" s="7" t="n"/>
+      <c r="C268" s="7" t="n"/>
+      <c r="D268" s="7" t="n"/>
+      <c r="E268" s="7" t="n"/>
+      <c r="F268" s="7" t="n"/>
+      <c r="G268" s="7" t="n"/>
+      <c r="H268" s="7">
+        <f>IF(E268="Consumo",IFERROR(D268*VLOOKUP(VLOOKUP(C268,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C268,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F268*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G268*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I268" s="7" t="n"/>
+      <c r="J268" s="7" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="7" t="n"/>
+      <c r="B269" s="7" t="n"/>
+      <c r="C269" s="7" t="n"/>
+      <c r="D269" s="7" t="n"/>
+      <c r="E269" s="7" t="n"/>
+      <c r="F269" s="7" t="n"/>
+      <c r="G269" s="7" t="n"/>
+      <c r="H269" s="7">
+        <f>IF(E269="Consumo",IFERROR(D269*VLOOKUP(VLOOKUP(C269,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C269,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F269*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G269*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I269" s="7" t="n"/>
+      <c r="J269" s="7" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="n"/>
+      <c r="B270" s="7" t="n"/>
+      <c r="C270" s="7" t="n"/>
+      <c r="D270" s="7" t="n"/>
+      <c r="E270" s="7" t="n"/>
+      <c r="F270" s="7" t="n"/>
+      <c r="G270" s="7" t="n"/>
+      <c r="H270" s="7">
+        <f>IF(E270="Consumo",IFERROR(D270*VLOOKUP(VLOOKUP(C270,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C270,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F270*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G270*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I270" s="7" t="n"/>
+      <c r="J270" s="7" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="7" t="n"/>
+      <c r="B271" s="7" t="n"/>
+      <c r="C271" s="7" t="n"/>
+      <c r="D271" s="7" t="n"/>
+      <c r="E271" s="7" t="n"/>
+      <c r="F271" s="7" t="n"/>
+      <c r="G271" s="7" t="n"/>
+      <c r="H271" s="7">
+        <f>IF(E271="Consumo",IFERROR(D271*VLOOKUP(VLOOKUP(C271,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C271,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F271*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G271*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I271" s="7" t="n"/>
+      <c r="J271" s="7" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="7" t="n"/>
+      <c r="B272" s="7" t="n"/>
+      <c r="C272" s="7" t="n"/>
+      <c r="D272" s="7" t="n"/>
+      <c r="E272" s="7" t="n"/>
+      <c r="F272" s="7" t="n"/>
+      <c r="G272" s="7" t="n"/>
+      <c r="H272" s="7">
+        <f>IF(E272="Consumo",IFERROR(D272*VLOOKUP(VLOOKUP(C272,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C272,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F272*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G272*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I272" s="7" t="n"/>
+      <c r="J272" s="7" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="7" t="n"/>
+      <c r="B273" s="7" t="n"/>
+      <c r="C273" s="7" t="n"/>
+      <c r="D273" s="7" t="n"/>
+      <c r="E273" s="7" t="n"/>
+      <c r="F273" s="7" t="n"/>
+      <c r="G273" s="7" t="n"/>
+      <c r="H273" s="7">
+        <f>IF(E273="Consumo",IFERROR(D273*VLOOKUP(VLOOKUP(C273,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C273,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F273*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G273*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I273" s="7" t="n"/>
+      <c r="J273" s="7" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="7" t="n"/>
+      <c r="B274" s="7" t="n"/>
+      <c r="C274" s="7" t="n"/>
+      <c r="D274" s="7" t="n"/>
+      <c r="E274" s="7" t="n"/>
+      <c r="F274" s="7" t="n"/>
+      <c r="G274" s="7" t="n"/>
+      <c r="H274" s="7">
+        <f>IF(E274="Consumo",IFERROR(D274*VLOOKUP(VLOOKUP(C274,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C274,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F274*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G274*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I274" s="7" t="n"/>
+      <c r="J274" s="7" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="7" t="n"/>
+      <c r="B275" s="7" t="n"/>
+      <c r="C275" s="7" t="n"/>
+      <c r="D275" s="7" t="n"/>
+      <c r="E275" s="7" t="n"/>
+      <c r="F275" s="7" t="n"/>
+      <c r="G275" s="7" t="n"/>
+      <c r="H275" s="7">
+        <f>IF(E275="Consumo",IFERROR(D275*VLOOKUP(VLOOKUP(C275,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C275,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F275*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G275*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I275" s="7" t="n"/>
+      <c r="J275" s="7" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="7" t="n"/>
+      <c r="B276" s="7" t="n"/>
+      <c r="C276" s="7" t="n"/>
+      <c r="D276" s="7" t="n"/>
+      <c r="E276" s="7" t="n"/>
+      <c r="F276" s="7" t="n"/>
+      <c r="G276" s="7" t="n"/>
+      <c r="H276" s="7">
+        <f>IF(E276="Consumo",IFERROR(D276*VLOOKUP(VLOOKUP(C276,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C276,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F276*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G276*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I276" s="7" t="n"/>
+      <c r="J276" s="7" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="7" t="n"/>
+      <c r="B277" s="7" t="n"/>
+      <c r="C277" s="7" t="n"/>
+      <c r="D277" s="7" t="n"/>
+      <c r="E277" s="7" t="n"/>
+      <c r="F277" s="7" t="n"/>
+      <c r="G277" s="7" t="n"/>
+      <c r="H277" s="7">
+        <f>IF(E277="Consumo",IFERROR(D277*VLOOKUP(VLOOKUP(C277,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C277,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F277*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G277*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I277" s="7" t="n"/>
+      <c r="J277" s="7" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="7" t="n"/>
+      <c r="B278" s="7" t="n"/>
+      <c r="C278" s="7" t="n"/>
+      <c r="D278" s="7" t="n"/>
+      <c r="E278" s="7" t="n"/>
+      <c r="F278" s="7" t="n"/>
+      <c r="G278" s="7" t="n"/>
+      <c r="H278" s="7">
+        <f>IF(E278="Consumo",IFERROR(D278*VLOOKUP(VLOOKUP(C278,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C278,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F278*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G278*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I278" s="7" t="n"/>
+      <c r="J278" s="7" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="n"/>
+      <c r="B279" s="7" t="n"/>
+      <c r="C279" s="7" t="n"/>
+      <c r="D279" s="7" t="n"/>
+      <c r="E279" s="7" t="n"/>
+      <c r="F279" s="7" t="n"/>
+      <c r="G279" s="7" t="n"/>
+      <c r="H279" s="7">
+        <f>IF(E279="Consumo",IFERROR(D279*VLOOKUP(VLOOKUP(C279,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C279,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F279*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G279*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I279" s="7" t="n"/>
+      <c r="J279" s="7" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="7" t="n"/>
+      <c r="B280" s="7" t="n"/>
+      <c r="C280" s="7" t="n"/>
+      <c r="D280" s="7" t="n"/>
+      <c r="E280" s="7" t="n"/>
+      <c r="F280" s="7" t="n"/>
+      <c r="G280" s="7" t="n"/>
+      <c r="H280" s="7">
+        <f>IF(E280="Consumo",IFERROR(D280*VLOOKUP(VLOOKUP(C280,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C280,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F280*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G280*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I280" s="7" t="n"/>
+      <c r="J280" s="7" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="7" t="n"/>
+      <c r="B281" s="7" t="n"/>
+      <c r="C281" s="7" t="n"/>
+      <c r="D281" s="7" t="n"/>
+      <c r="E281" s="7" t="n"/>
+      <c r="F281" s="7" t="n"/>
+      <c r="G281" s="7" t="n"/>
+      <c r="H281" s="7">
+        <f>IF(E281="Consumo",IFERROR(D281*VLOOKUP(VLOOKUP(C281,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C281,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F281*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G281*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I281" s="7" t="n"/>
+      <c r="J281" s="7" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="7" t="n"/>
+      <c r="B282" s="7" t="n"/>
+      <c r="C282" s="7" t="n"/>
+      <c r="D282" s="7" t="n"/>
+      <c r="E282" s="7" t="n"/>
+      <c r="F282" s="7" t="n"/>
+      <c r="G282" s="7" t="n"/>
+      <c r="H282" s="7">
+        <f>IF(E282="Consumo",IFERROR(D282*VLOOKUP(VLOOKUP(C282,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C282,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F282*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G282*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I282" s="7" t="n"/>
+      <c r="J282" s="7" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="7" t="n"/>
+      <c r="B283" s="7" t="n"/>
+      <c r="C283" s="7" t="n"/>
+      <c r="D283" s="7" t="n"/>
+      <c r="E283" s="7" t="n"/>
+      <c r="F283" s="7" t="n"/>
+      <c r="G283" s="7" t="n"/>
+      <c r="H283" s="7">
+        <f>IF(E283="Consumo",IFERROR(D283*VLOOKUP(VLOOKUP(C283,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C283,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F283*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G283*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I283" s="7" t="n"/>
+      <c r="J283" s="7" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="7" t="n"/>
+      <c r="B284" s="7" t="n"/>
+      <c r="C284" s="7" t="n"/>
+      <c r="D284" s="7" t="n"/>
+      <c r="E284" s="7" t="n"/>
+      <c r="F284" s="7" t="n"/>
+      <c r="G284" s="7" t="n"/>
+      <c r="H284" s="7">
+        <f>IF(E284="Consumo",IFERROR(D284*VLOOKUP(VLOOKUP(C284,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C284,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F284*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G284*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I284" s="7" t="n"/>
+      <c r="J284" s="7" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="n"/>
+      <c r="B285" s="7" t="n"/>
+      <c r="C285" s="7" t="n"/>
+      <c r="D285" s="7" t="n"/>
+      <c r="E285" s="7" t="n"/>
+      <c r="F285" s="7" t="n"/>
+      <c r="G285" s="7" t="n"/>
+      <c r="H285" s="7">
+        <f>IF(E285="Consumo",IFERROR(D285*VLOOKUP(VLOOKUP(C285,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C285,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F285*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G285*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I285" s="7" t="n"/>
+      <c r="J285" s="7" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="7" t="n"/>
+      <c r="B286" s="7" t="n"/>
+      <c r="C286" s="7" t="n"/>
+      <c r="D286" s="7" t="n"/>
+      <c r="E286" s="7" t="n"/>
+      <c r="F286" s="7" t="n"/>
+      <c r="G286" s="7" t="n"/>
+      <c r="H286" s="7">
+        <f>IF(E286="Consumo",IFERROR(D286*VLOOKUP(VLOOKUP(C286,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C286,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F286*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G286*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I286" s="7" t="n"/>
+      <c r="J286" s="7" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="7" t="n"/>
+      <c r="B287" s="7" t="n"/>
+      <c r="C287" s="7" t="n"/>
+      <c r="D287" s="7" t="n"/>
+      <c r="E287" s="7" t="n"/>
+      <c r="F287" s="7" t="n"/>
+      <c r="G287" s="7" t="n"/>
+      <c r="H287" s="7">
+        <f>IF(E287="Consumo",IFERROR(D287*VLOOKUP(VLOOKUP(C287,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C287,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F287*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G287*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I287" s="7" t="n"/>
+      <c r="J287" s="7" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="7" t="n"/>
+      <c r="B288" s="7" t="n"/>
+      <c r="C288" s="7" t="n"/>
+      <c r="D288" s="7" t="n"/>
+      <c r="E288" s="7" t="n"/>
+      <c r="F288" s="7" t="n"/>
+      <c r="G288" s="7" t="n"/>
+      <c r="H288" s="7">
+        <f>IF(E288="Consumo",IFERROR(D288*VLOOKUP(VLOOKUP(C288,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C288,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F288*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G288*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I288" s="7" t="n"/>
+      <c r="J288" s="7" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="n"/>
+      <c r="B289" s="7" t="n"/>
+      <c r="C289" s="7" t="n"/>
+      <c r="D289" s="7" t="n"/>
+      <c r="E289" s="7" t="n"/>
+      <c r="F289" s="7" t="n"/>
+      <c r="G289" s="7" t="n"/>
+      <c r="H289" s="7">
+        <f>IF(E289="Consumo",IFERROR(D289*VLOOKUP(VLOOKUP(C289,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C289,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F289*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G289*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I289" s="7" t="n"/>
+      <c r="J289" s="7" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="7" t="n"/>
+      <c r="B290" s="7" t="n"/>
+      <c r="C290" s="7" t="n"/>
+      <c r="D290" s="7" t="n"/>
+      <c r="E290" s="7" t="n"/>
+      <c r="F290" s="7" t="n"/>
+      <c r="G290" s="7" t="n"/>
+      <c r="H290" s="7">
+        <f>IF(E290="Consumo",IFERROR(D290*VLOOKUP(VLOOKUP(C290,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C290,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F290*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G290*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I290" s="7" t="n"/>
+      <c r="J290" s="7" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="n"/>
+      <c r="B291" s="7" t="n"/>
+      <c r="C291" s="7" t="n"/>
+      <c r="D291" s="7" t="n"/>
+      <c r="E291" s="7" t="n"/>
+      <c r="F291" s="7" t="n"/>
+      <c r="G291" s="7" t="n"/>
+      <c r="H291" s="7">
+        <f>IF(E291="Consumo",IFERROR(D291*VLOOKUP(VLOOKUP(C291,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C291,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F291*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G291*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I291" s="7" t="n"/>
+      <c r="J291" s="7" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="n"/>
+      <c r="B292" s="7" t="n"/>
+      <c r="C292" s="7" t="n"/>
+      <c r="D292" s="7" t="n"/>
+      <c r="E292" s="7" t="n"/>
+      <c r="F292" s="7" t="n"/>
+      <c r="G292" s="7" t="n"/>
+      <c r="H292" s="7">
+        <f>IF(E292="Consumo",IFERROR(D292*VLOOKUP(VLOOKUP(C292,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C292,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F292*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G292*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I292" s="7" t="n"/>
+      <c r="J292" s="7" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="7" t="n"/>
+      <c r="B293" s="7" t="n"/>
+      <c r="C293" s="7" t="n"/>
+      <c r="D293" s="7" t="n"/>
+      <c r="E293" s="7" t="n"/>
+      <c r="F293" s="7" t="n"/>
+      <c r="G293" s="7" t="n"/>
+      <c r="H293" s="7">
+        <f>IF(E293="Consumo",IFERROR(D293*VLOOKUP(VLOOKUP(C293,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C293,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F293*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G293*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I293" s="7" t="n"/>
+      <c r="J293" s="7" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="7" t="n"/>
+      <c r="B294" s="7" t="n"/>
+      <c r="C294" s="7" t="n"/>
+      <c r="D294" s="7" t="n"/>
+      <c r="E294" s="7" t="n"/>
+      <c r="F294" s="7" t="n"/>
+      <c r="G294" s="7" t="n"/>
+      <c r="H294" s="7">
+        <f>IF(E294="Consumo",IFERROR(D294*VLOOKUP(VLOOKUP(C294,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C294,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F294*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G294*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I294" s="7" t="n"/>
+      <c r="J294" s="7" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="n"/>
+      <c r="B295" s="7" t="n"/>
+      <c r="C295" s="7" t="n"/>
+      <c r="D295" s="7" t="n"/>
+      <c r="E295" s="7" t="n"/>
+      <c r="F295" s="7" t="n"/>
+      <c r="G295" s="7" t="n"/>
+      <c r="H295" s="7">
+        <f>IF(E295="Consumo",IFERROR(D295*VLOOKUP(VLOOKUP(C295,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C295,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F295*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G295*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I295" s="7" t="n"/>
+      <c r="J295" s="7" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="7" t="n"/>
+      <c r="B296" s="7" t="n"/>
+      <c r="C296" s="7" t="n"/>
+      <c r="D296" s="7" t="n"/>
+      <c r="E296" s="7" t="n"/>
+      <c r="F296" s="7" t="n"/>
+      <c r="G296" s="7" t="n"/>
+      <c r="H296" s="7">
+        <f>IF(E296="Consumo",IFERROR(D296*VLOOKUP(VLOOKUP(C296,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C296,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F296*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G296*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I296" s="7" t="n"/>
+      <c r="J296" s="7" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="7" t="n"/>
+      <c r="B297" s="7" t="n"/>
+      <c r="C297" s="7" t="n"/>
+      <c r="D297" s="7" t="n"/>
+      <c r="E297" s="7" t="n"/>
+      <c r="F297" s="7" t="n"/>
+      <c r="G297" s="7" t="n"/>
+      <c r="H297" s="7">
+        <f>IF(E297="Consumo",IFERROR(D297*VLOOKUP(VLOOKUP(C297,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C297,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F297*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G297*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I297" s="7" t="n"/>
+      <c r="J297" s="7" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="7" t="n"/>
+      <c r="B298" s="7" t="n"/>
+      <c r="C298" s="7" t="n"/>
+      <c r="D298" s="7" t="n"/>
+      <c r="E298" s="7" t="n"/>
+      <c r="F298" s="7" t="n"/>
+      <c r="G298" s="7" t="n"/>
+      <c r="H298" s="7">
+        <f>IF(E298="Consumo",IFERROR(D298*VLOOKUP(VLOOKUP(C298,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C298,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F298*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G298*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I298" s="7" t="n"/>
+      <c r="J298" s="7" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="7" t="n"/>
+      <c r="B299" s="7" t="n"/>
+      <c r="C299" s="7" t="n"/>
+      <c r="D299" s="7" t="n"/>
+      <c r="E299" s="7" t="n"/>
+      <c r="F299" s="7" t="n"/>
+      <c r="G299" s="7" t="n"/>
+      <c r="H299" s="7">
+        <f>IF(E299="Consumo",IFERROR(D299*VLOOKUP(VLOOKUP(C299,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C299,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F299*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G299*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I299" s="7" t="n"/>
+      <c r="J299" s="7" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="7" t="n"/>
+      <c r="B300" s="7" t="n"/>
+      <c r="C300" s="7" t="n"/>
+      <c r="D300" s="7" t="n"/>
+      <c r="E300" s="7" t="n"/>
+      <c r="F300" s="7" t="n"/>
+      <c r="G300" s="7" t="n"/>
+      <c r="H300" s="7">
+        <f>IF(E300="Consumo",IFERROR(D300*VLOOKUP(VLOOKUP(C300,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C300,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F300*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G300*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I300" s="7" t="n"/>
+      <c r="J300" s="7" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="7" t="n"/>
+      <c r="B301" s="7" t="n"/>
+      <c r="C301" s="7" t="n"/>
+      <c r="D301" s="7" t="n"/>
+      <c r="E301" s="7" t="n"/>
+      <c r="F301" s="7" t="n"/>
+      <c r="G301" s="7" t="n"/>
+      <c r="H301" s="7">
+        <f>IF(E301="Consumo",IFERROR(D301*VLOOKUP(VLOOKUP(C301,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C301,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F301*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G301*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I301" s="7" t="n"/>
+      <c r="J301" s="7" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="7" t="n"/>
+      <c r="B302" s="7" t="n"/>
+      <c r="C302" s="7" t="n"/>
+      <c r="D302" s="7" t="n"/>
+      <c r="E302" s="7" t="n"/>
+      <c r="F302" s="7" t="n"/>
+      <c r="G302" s="7" t="n"/>
+      <c r="H302" s="7">
+        <f>IF(E302="Consumo",IFERROR(D302*VLOOKUP(VLOOKUP(C302,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C302,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F302*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G302*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I302" s="7" t="n"/>
+      <c r="J302" s="7" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="7" t="n"/>
+      <c r="B303" s="7" t="n"/>
+      <c r="C303" s="7" t="n"/>
+      <c r="D303" s="7" t="n"/>
+      <c r="E303" s="7" t="n"/>
+      <c r="F303" s="7" t="n"/>
+      <c r="G303" s="7" t="n"/>
+      <c r="H303" s="7">
+        <f>IF(E303="Consumo",IFERROR(D303*VLOOKUP(VLOOKUP(C303,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C303,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F303*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G303*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I303" s="7" t="n"/>
+      <c r="J303" s="7" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="7" t="n"/>
+      <c r="B304" s="7" t="n"/>
+      <c r="C304" s="7" t="n"/>
+      <c r="D304" s="7" t="n"/>
+      <c r="E304" s="7" t="n"/>
+      <c r="F304" s="7" t="n"/>
+      <c r="G304" s="7" t="n"/>
+      <c r="H304" s="7">
+        <f>IF(E304="Consumo",IFERROR(D304*VLOOKUP(VLOOKUP(C304,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C304,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F304*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G304*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I304" s="7" t="n"/>
+      <c r="J304" s="7" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="n"/>
+      <c r="B305" s="7" t="n"/>
+      <c r="C305" s="7" t="n"/>
+      <c r="D305" s="7" t="n"/>
+      <c r="E305" s="7" t="n"/>
+      <c r="F305" s="7" t="n"/>
+      <c r="G305" s="7" t="n"/>
+      <c r="H305" s="7">
+        <f>IF(E305="Consumo",IFERROR(D305*VLOOKUP(VLOOKUP(C305,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C305,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F305*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G305*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I305" s="7" t="n"/>
+      <c r="J305" s="7" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="7" t="n"/>
+      <c r="B306" s="7" t="n"/>
+      <c r="C306" s="7" t="n"/>
+      <c r="D306" s="7" t="n"/>
+      <c r="E306" s="7" t="n"/>
+      <c r="F306" s="7" t="n"/>
+      <c r="G306" s="7" t="n"/>
+      <c r="H306" s="7">
+        <f>IF(E306="Consumo",IFERROR(D306*VLOOKUP(VLOOKUP(C306,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C306,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F306*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G306*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I306" s="7" t="n"/>
+      <c r="J306" s="7" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="7" t="n"/>
+      <c r="B307" s="7" t="n"/>
+      <c r="C307" s="7" t="n"/>
+      <c r="D307" s="7" t="n"/>
+      <c r="E307" s="7" t="n"/>
+      <c r="F307" s="7" t="n"/>
+      <c r="G307" s="7" t="n"/>
+      <c r="H307" s="7">
+        <f>IF(E307="Consumo",IFERROR(D307*VLOOKUP(VLOOKUP(C307,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C307,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F307*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G307*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I307" s="7" t="n"/>
+      <c r="J307" s="7" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="7" t="n"/>
+      <c r="B308" s="7" t="n"/>
+      <c r="C308" s="7" t="n"/>
+      <c r="D308" s="7" t="n"/>
+      <c r="E308" s="7" t="n"/>
+      <c r="F308" s="7" t="n"/>
+      <c r="G308" s="7" t="n"/>
+      <c r="H308" s="7">
+        <f>IF(E308="Consumo",IFERROR(D308*VLOOKUP(VLOOKUP(C308,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C308,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F308*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G308*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I308" s="7" t="n"/>
+      <c r="J308" s="7" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="7" t="n"/>
+      <c r="B309" s="7" t="n"/>
+      <c r="C309" s="7" t="n"/>
+      <c r="D309" s="7" t="n"/>
+      <c r="E309" s="7" t="n"/>
+      <c r="F309" s="7" t="n"/>
+      <c r="G309" s="7" t="n"/>
+      <c r="H309" s="7">
+        <f>IF(E309="Consumo",IFERROR(D309*VLOOKUP(VLOOKUP(C309,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C309,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F309*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G309*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I309" s="7" t="n"/>
+      <c r="J309" s="7" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="7" t="n"/>
+      <c r="B310" s="7" t="n"/>
+      <c r="C310" s="7" t="n"/>
+      <c r="D310" s="7" t="n"/>
+      <c r="E310" s="7" t="n"/>
+      <c r="F310" s="7" t="n"/>
+      <c r="G310" s="7" t="n"/>
+      <c r="H310" s="7">
+        <f>IF(E310="Consumo",IFERROR(D310*VLOOKUP(VLOOKUP(C310,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C310,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F310*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G310*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I310" s="7" t="n"/>
+      <c r="J310" s="7" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="7" t="n"/>
+      <c r="B311" s="7" t="n"/>
+      <c r="C311" s="7" t="n"/>
+      <c r="D311" s="7" t="n"/>
+      <c r="E311" s="7" t="n"/>
+      <c r="F311" s="7" t="n"/>
+      <c r="G311" s="7" t="n"/>
+      <c r="H311" s="7">
+        <f>IF(E311="Consumo",IFERROR(D311*VLOOKUP(VLOOKUP(C311,ConfigBuffet!$C:$D,2,FALSE),Precios!$A:$C,3,FALSE)*VLOOKUP(C311,ConfigBuffet!$C:$F,4,FALSE),0)+IFERROR(F311*VLOOKUP("b06",Precios!$A:$C,3,FALSE),0)+IFERROR(G311*VLOOKUP("b28",Precios!$A:$C,3,FALSE),0),0)</f>
+        <v/>
+      </c>
+      <c r="I311" s="7" t="n"/>
+      <c r="J311" s="7" t="n"/>
+    </row>
+    <row r="313">
+      <c r="G313" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H313" s="13">
+        <f>SUM(H2:H312)</f>
         <v/>
       </c>
     </row>
@@ -21596,4 +24196,1023 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Cantidad ↑↓</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Importado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n"/>
+      <c r="B78" s="7" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="7" t="n"/>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n"/>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n"/>
+      <c r="B80" s="7" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n"/>
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n"/>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="7" t="n"/>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n"/>
+      <c r="B84" s="7" t="n"/>
+      <c r="C84" s="7" t="n"/>
+      <c r="D84" s="7" t="n"/>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="7" t="n"/>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n"/>
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n"/>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+      <c r="E94" s="7" t="n"/>
+      <c r="F94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n"/>
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="7" t="n"/>
+      <c r="F96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n"/>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n"/>
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
+      <c r="E100" s="7" t="n"/>
+      <c r="F100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n"/>
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
+      <c r="E102" s="7" t="n"/>
+      <c r="F102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n"/>
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n"/>
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
+      <c r="E104" s="7" t="n"/>
+      <c r="F104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n"/>
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n"/>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n"/>
+      <c r="B108" s="7" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n"/>
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="7" t="n"/>
+      <c r="E109" s="7" t="n"/>
+      <c r="F109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="7" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+      <c r="E110" s="7" t="n"/>
+      <c r="F110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n"/>
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+      <c r="E111" s="7" t="n"/>
+      <c r="F111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n"/>
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n"/>
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n"/>
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n"/>
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n"/>
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n"/>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n"/>
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="n"/>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n"/>
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="n"/>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Receta,Extra,Producto"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Catalogo!$I$2:$I$25</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>